--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_hospitals_healthcare_facilities.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2035275761892282</v>
+        <v>0.2032521293097065</v>
       </c>
       <c r="C2">
-        <v>17.80094411710082</v>
+        <v>17.66766292891517</v>
       </c>
       <c r="D2">
-        <v>17.67394411710082</v>
+        <v>17.70486292891517</v>
       </c>
       <c r="E2">
-        <v>-1.82</v>
+        <v>-1.6558</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1642</v>
       </c>
       <c r="G2">
         <v>0.127</v>
@@ -1439,45 +1439,45 @@
         <v>0.061</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00891606</v>
       </c>
       <c r="N2">
-        <v>0.061</v>
+        <v>0.05208394</v>
       </c>
       <c r="O2">
-        <v>0.01037</v>
+        <v>0.0088542698</v>
       </c>
       <c r="P2">
-        <v>0.05062999999999999</v>
+        <v>0.04322967019999999</v>
       </c>
       <c r="Q2">
-        <v>0.50663</v>
+        <v>0.4992296702</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2035275761892282</v>
+        <v>0.2048499386966733</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5696087073363274</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0543</v>
       </c>
       <c r="V2">
         <v>0.17</v>
       </c>
       <c r="W2">
-        <v>0.04174899999999999</v>
+        <v>0.045069</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>6.841586979001935</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2032521293097065</v>
+        <v>0.2032688424301848</v>
       </c>
       <c r="C3">
-        <v>17.66766292891517</v>
+        <v>17.50158380474929</v>
       </c>
       <c r="D3">
-        <v>17.70486292891517</v>
+        <v>17.70298380474929</v>
       </c>
       <c r="E3">
-        <v>-1.6558</v>
+        <v>-1.4916</v>
       </c>
       <c r="F3">
-        <v>0.1642</v>
+        <v>0.3284</v>
       </c>
       <c r="G3">
         <v>0.127</v>
@@ -1521,45 +1521,45 @@
         <v>0.061</v>
       </c>
       <c r="M3">
-        <v>0.00891606</v>
+        <v>0.02361196</v>
       </c>
       <c r="N3">
-        <v>0.05208394</v>
+        <v>0.03738804</v>
       </c>
       <c r="O3">
-        <v>0.0088542698</v>
+        <v>0.0063559668</v>
       </c>
       <c r="P3">
-        <v>0.04322967019999999</v>
+        <v>0.0310320732</v>
       </c>
       <c r="Q3">
-        <v>0.4992296702</v>
+        <v>0.4870320732</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2048499386966733</v>
+        <v>0.2061992881940662</v>
       </c>
       <c r="T3">
-        <v>0.5696087073363274</v>
+        <v>0.5744411595161469</v>
       </c>
       <c r="U3">
-        <v>0.0543</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V3">
         <v>0.17</v>
       </c>
       <c r="W3">
-        <v>0.045069</v>
+        <v>0.059677</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>6.841586979001935</v>
+        <v>2.583436529623123</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2032688424301848</v>
+        <v>0.2052474709788106</v>
       </c>
       <c r="C4">
-        <v>17.50158380474929</v>
+        <v>17.11770249568299</v>
       </c>
       <c r="D4">
-        <v>17.70298380474929</v>
+        <v>17.48330249568299</v>
       </c>
       <c r="E4">
-        <v>-1.4916</v>
+        <v>-1.3274</v>
       </c>
       <c r="F4">
-        <v>0.3284</v>
+        <v>0.4925999999999999</v>
       </c>
       <c r="G4">
         <v>0.127</v>
@@ -1603,45 +1603,45 @@
         <v>0.061</v>
       </c>
       <c r="M4">
-        <v>0.02361196</v>
+        <v>0.07231367999999999</v>
       </c>
       <c r="N4">
-        <v>0.03738804</v>
+        <v>-0.01131367999999999</v>
       </c>
       <c r="O4">
-        <v>0.0063559668</v>
+        <v>-0.001923325599999999</v>
       </c>
       <c r="P4">
-        <v>0.0310320732</v>
+        <v>-0.009390354399999993</v>
       </c>
       <c r="Q4">
-        <v>0.4870320732</v>
+        <v>0.4466096456</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2061992881940662</v>
+        <v>0.2077062039926209</v>
       </c>
       <c r="T4">
-        <v>0.5744411595161469</v>
+        <v>0.5798379070227049</v>
       </c>
       <c r="U4">
-        <v>0.07190000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V4">
-        <v>0.17</v>
+        <v>0.1434030186266278</v>
       </c>
       <c r="W4">
-        <v>0.059677</v>
+        <v>0.125748436865611</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y4">
-        <v>2.583436529623123</v>
+        <v>0.8435471683919281</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2052474709788106</v>
+        <v>0.2100735850168019</v>
       </c>
       <c r="C5">
-        <v>17.11770249568299</v>
+        <v>16.43986902505389</v>
       </c>
       <c r="D5">
-        <v>17.48330249568299</v>
+        <v>16.96966902505389</v>
       </c>
       <c r="E5">
-        <v>-1.3274</v>
+        <v>-1.1632</v>
       </c>
       <c r="F5">
-        <v>0.4925999999999999</v>
+        <v>0.6567999999999999</v>
       </c>
       <c r="G5">
         <v>0.127</v>
@@ -1685,45 +1685,45 @@
         <v>0.061</v>
       </c>
       <c r="M5">
-        <v>0.07231367999999999</v>
+        <v>0.15487344</v>
       </c>
       <c r="N5">
-        <v>-0.01131367999999999</v>
+        <v>-0.09387344</v>
       </c>
       <c r="O5">
-        <v>-0.001923325599999999</v>
+        <v>-0.0159584848</v>
       </c>
       <c r="P5">
-        <v>-0.009390354399999993</v>
+        <v>-0.0779149552</v>
       </c>
       <c r="Q5">
-        <v>0.4466096456</v>
+        <v>0.3780850448</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2077062039926209</v>
+        <v>0.2096595124071183</v>
       </c>
       <c r="T5">
-        <v>0.5798379070227049</v>
+        <v>0.5868333292789368</v>
       </c>
       <c r="U5">
-        <v>0.1468</v>
+        <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>0.1434030186266278</v>
+        <v>0.066957898010143</v>
       </c>
       <c r="W5">
-        <v>0.125748436865611</v>
+        <v>0.2200113276492083</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y5">
-        <v>0.8435471683919281</v>
+        <v>0.3938699882949588</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2100735850168019</v>
+        <v>0.2119735850168019</v>
       </c>
       <c r="C6">
-        <v>16.43986902505389</v>
+        <v>16.08164076752823</v>
       </c>
       <c r="D6">
-        <v>16.96966902505389</v>
+        <v>16.77564076752823</v>
       </c>
       <c r="E6">
-        <v>-1.1632</v>
+        <v>-0.9990000000000001</v>
       </c>
       <c r="F6">
-        <v>0.6567999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="G6">
         <v>0.127</v>
@@ -1767,37 +1767,37 @@
         <v>0.061</v>
       </c>
       <c r="M6">
-        <v>0.15487344</v>
+        <v>0.1935918</v>
       </c>
       <c r="N6">
-        <v>-0.09387344</v>
+        <v>-0.1325918</v>
       </c>
       <c r="O6">
-        <v>-0.0159584848</v>
+        <v>-0.022540606</v>
       </c>
       <c r="P6">
-        <v>-0.0779149552</v>
+        <v>-0.110051194</v>
       </c>
       <c r="Q6">
-        <v>0.3780850448</v>
+        <v>0.345948806</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2096595124071183</v>
+        <v>0.2113843493798248</v>
       </c>
       <c r="T6">
-        <v>0.5868333292789368</v>
+        <v>0.5930105222187151</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.066957898010143</v>
+        <v>0.05356631840811439</v>
       </c>
       <c r="W6">
-        <v>0.2200113276492083</v>
+        <v>0.2231690621193666</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.3938699882949588</v>
+        <v>0.315095990635967</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2119735850168019</v>
+        <v>0.2138735850168019</v>
       </c>
       <c r="C7">
-        <v>16.08164076752823</v>
+        <v>15.72779932294836</v>
       </c>
       <c r="D7">
-        <v>16.77564076752823</v>
+        <v>16.58599932294836</v>
       </c>
       <c r="E7">
-        <v>-0.9990000000000001</v>
+        <v>-0.8348000000000001</v>
       </c>
       <c r="F7">
-        <v>0.821</v>
+        <v>0.9852</v>
       </c>
       <c r="G7">
         <v>0.127</v>
@@ -1849,37 +1849,37 @@
         <v>0.061</v>
       </c>
       <c r="M7">
-        <v>0.1935918</v>
+        <v>0.23231016</v>
       </c>
       <c r="N7">
-        <v>-0.1325918</v>
+        <v>-0.17131016</v>
       </c>
       <c r="O7">
-        <v>-0.022540606</v>
+        <v>-0.0291227272</v>
       </c>
       <c r="P7">
-        <v>-0.110051194</v>
+        <v>-0.1421874328</v>
       </c>
       <c r="Q7">
-        <v>0.345948806</v>
+        <v>0.3138125672000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2113843493798248</v>
+        <v>0.2131458850115251</v>
       </c>
       <c r="T7">
-        <v>0.5930105222187151</v>
+        <v>0.59931914479551</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.05356631840811439</v>
+        <v>0.04463859867342867</v>
       </c>
       <c r="W7">
-        <v>0.2231690621193666</v>
+        <v>0.2252742184328055</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.315095990635967</v>
+        <v>0.2625799921966392</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2138735850168019</v>
+        <v>0.2157735850168019</v>
       </c>
       <c r="C8">
-        <v>15.72779932294836</v>
+        <v>15.37819758119839</v>
       </c>
       <c r="D8">
-        <v>16.58599932294836</v>
+        <v>16.40059758119839</v>
       </c>
       <c r="E8">
-        <v>-0.8348000000000002</v>
+        <v>-0.6706000000000003</v>
       </c>
       <c r="F8">
-        <v>0.9851999999999999</v>
+        <v>1.1494</v>
       </c>
       <c r="G8">
         <v>0.127</v>
@@ -1931,37 +1931,37 @@
         <v>0.061</v>
       </c>
       <c r="M8">
-        <v>0.23231016</v>
+        <v>0.2710285199999999</v>
       </c>
       <c r="N8">
-        <v>-0.17131016</v>
+        <v>-0.2100285199999999</v>
       </c>
       <c r="O8">
-        <v>-0.0291227272</v>
+        <v>-0.0357048484</v>
       </c>
       <c r="P8">
-        <v>-0.1421874328</v>
+        <v>-0.1743236716</v>
       </c>
       <c r="Q8">
-        <v>0.3138125672000001</v>
+        <v>0.2816763284000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2131458850115251</v>
+        <v>0.2149453031299286</v>
       </c>
       <c r="T8">
-        <v>0.59931914479551</v>
+        <v>0.6057634366750315</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.04463859867342867</v>
+        <v>0.03826165600579601</v>
       </c>
       <c r="W8">
-        <v>0.2252742184328055</v>
+        <v>0.2267779015138333</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.2625799921966392</v>
+        <v>0.2250685647399765</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2157735850168019</v>
+        <v>0.2176735850168019</v>
       </c>
       <c r="C9">
-        <v>15.37819758119839</v>
+        <v>15.03269493715783</v>
       </c>
       <c r="D9">
-        <v>16.40059758119839</v>
+        <v>16.21929493715783</v>
       </c>
       <c r="E9">
-        <v>-0.6706000000000001</v>
+        <v>-0.5064000000000002</v>
       </c>
       <c r="F9">
-        <v>1.1494</v>
+        <v>1.3136</v>
       </c>
       <c r="G9">
         <v>0.127</v>
@@ -2013,37 +2013,37 @@
         <v>0.061</v>
       </c>
       <c r="M9">
-        <v>0.27102852</v>
+        <v>0.30974688</v>
       </c>
       <c r="N9">
-        <v>-0.21002852</v>
+        <v>-0.24874688</v>
       </c>
       <c r="O9">
-        <v>-0.0357048484</v>
+        <v>-0.0422869696</v>
       </c>
       <c r="P9">
-        <v>-0.1743236716</v>
+        <v>-0.2064599104</v>
       </c>
       <c r="Q9">
-        <v>0.2816763284</v>
+        <v>0.2495400896</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2149453031299286</v>
+        <v>0.2167838390335148</v>
       </c>
       <c r="T9">
-        <v>0.6057634366750316</v>
+        <v>0.6123478218562819</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.038261656005796</v>
+        <v>0.0334789490050715</v>
       </c>
       <c r="W9">
-        <v>0.2267779015138333</v>
+        <v>0.2279056638246041</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.2250685647399765</v>
+        <v>0.1969349941474794</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2176735850168019</v>
+        <v>0.2195735850168019</v>
       </c>
       <c r="C10">
-        <v>15.03269493715783</v>
+        <v>14.69115693508104</v>
       </c>
       <c r="D10">
-        <v>16.21929493715783</v>
+        <v>16.04195693508105</v>
       </c>
       <c r="E10">
-        <v>-0.5064000000000002</v>
+        <v>-0.3422000000000003</v>
       </c>
       <c r="F10">
-        <v>1.3136</v>
+        <v>1.4778</v>
       </c>
       <c r="G10">
         <v>0.127</v>
@@ -2095,37 +2095,37 @@
         <v>0.061</v>
       </c>
       <c r="M10">
-        <v>0.30974688</v>
+        <v>0.34846524</v>
       </c>
       <c r="N10">
-        <v>-0.24874688</v>
+        <v>-0.28746524</v>
       </c>
       <c r="O10">
-        <v>-0.0422869696</v>
+        <v>-0.04886909079999999</v>
       </c>
       <c r="P10">
-        <v>-0.2064599104</v>
+        <v>-0.2385961492</v>
       </c>
       <c r="Q10">
-        <v>0.2495400896</v>
+        <v>0.2174038508</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2167838390335148</v>
+        <v>0.2186627823195973</v>
       </c>
       <c r="T10">
-        <v>0.6123478218562819</v>
+        <v>0.6190769187997575</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.0334789490050715</v>
+        <v>0.02975906578228578</v>
       </c>
       <c r="W10">
-        <v>0.2279056638246041</v>
+        <v>0.228782812288537</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.1969349941474794</v>
+        <v>0.1750533281310928</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2195735850168019</v>
+        <v>0.2214735850168019</v>
       </c>
       <c r="C11">
-        <v>14.69115693508104</v>
+        <v>14.35345493605405</v>
       </c>
       <c r="D11">
-        <v>16.04195693508105</v>
+        <v>15.86845493605405</v>
       </c>
       <c r="E11">
-        <v>-0.3422000000000003</v>
+        <v>-0.1780000000000004</v>
       </c>
       <c r="F11">
-        <v>1.4778</v>
+        <v>1.642</v>
       </c>
       <c r="G11">
         <v>0.127</v>
@@ -2177,37 +2177,37 @@
         <v>0.061</v>
       </c>
       <c r="M11">
-        <v>0.34846524</v>
+        <v>0.3871836</v>
       </c>
       <c r="N11">
-        <v>-0.28746524</v>
+        <v>-0.3261836</v>
       </c>
       <c r="O11">
-        <v>-0.04886909079999999</v>
+        <v>-0.055451212</v>
       </c>
       <c r="P11">
-        <v>-0.2385961492</v>
+        <v>-0.270732388</v>
       </c>
       <c r="Q11">
-        <v>0.2174038508</v>
+        <v>0.185267612</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2186627823195973</v>
+        <v>0.2205834799009262</v>
       </c>
       <c r="T11">
-        <v>0.6190769187997575</v>
+        <v>0.6259555512308659</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.02975906578228578</v>
+        <v>0.0267831592040572</v>
       </c>
       <c r="W11">
-        <v>0.228782812288537</v>
+        <v>0.2294845310596833</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.1750533281310928</v>
+        <v>0.1575479953179835</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2214735850168019</v>
+        <v>0.2233735850168019</v>
       </c>
       <c r="C12">
-        <v>14.35345493605405</v>
+        <v>14.01946580680011</v>
       </c>
       <c r="D12">
-        <v>15.86845493605405</v>
+        <v>15.69866580680011</v>
       </c>
       <c r="E12">
-        <v>-0.1780000000000002</v>
+        <v>-0.01380000000000026</v>
       </c>
       <c r="F12">
-        <v>1.642</v>
+        <v>1.8062</v>
       </c>
       <c r="G12">
         <v>0.127</v>
@@ -2259,37 +2259,37 @@
         <v>0.061</v>
       </c>
       <c r="M12">
-        <v>0.3871836</v>
+        <v>0.42590196</v>
       </c>
       <c r="N12">
-        <v>-0.3261836</v>
+        <v>-0.36490196</v>
       </c>
       <c r="O12">
-        <v>-0.05545121200000001</v>
+        <v>-0.0620333332</v>
       </c>
       <c r="P12">
-        <v>-0.270732388</v>
+        <v>-0.3028686268</v>
       </c>
       <c r="Q12">
-        <v>0.185267612</v>
+        <v>0.1531313732</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2205834799009262</v>
+        <v>0.2225473392256557</v>
       </c>
       <c r="T12">
-        <v>0.6259555512308659</v>
+        <v>0.6329887596716622</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.0267831592040572</v>
+        <v>0.02434832654914291</v>
       </c>
       <c r="W12">
-        <v>0.2294845310596833</v>
+        <v>0.2300586645997121</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.1575479953179835</v>
+        <v>0.143225450289076</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2233735850168019</v>
+        <v>0.2252735850168019</v>
       </c>
       <c r="C13">
-        <v>14.01946580680011</v>
+        <v>13.68907162825218</v>
       </c>
       <c r="D13">
-        <v>15.69866580680011</v>
+        <v>15.53247162825218</v>
       </c>
       <c r="E13">
-        <v>-0.01380000000000026</v>
+        <v>0.1503999999999996</v>
       </c>
       <c r="F13">
-        <v>1.8062</v>
+        <v>1.9704</v>
       </c>
       <c r="G13">
         <v>0.127</v>
@@ -2341,37 +2341,37 @@
         <v>0.061</v>
       </c>
       <c r="M13">
-        <v>0.42590196</v>
+        <v>0.46462032</v>
       </c>
       <c r="N13">
-        <v>-0.36490196</v>
+        <v>-0.40362032</v>
       </c>
       <c r="O13">
-        <v>-0.0620333332</v>
+        <v>-0.0686154544</v>
       </c>
       <c r="P13">
-        <v>-0.3028686268</v>
+        <v>-0.3350048656</v>
       </c>
       <c r="Q13">
-        <v>0.1531313732</v>
+        <v>0.1209951344</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2225473392256557</v>
+        <v>0.2245558317168564</v>
       </c>
       <c r="T13">
-        <v>0.6329887596716622</v>
+        <v>0.6401818137588402</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.02434832654914291</v>
+        <v>0.02231929933671433</v>
       </c>
       <c r="W13">
-        <v>0.2300586645997121</v>
+        <v>0.2305371092164028</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.143225450289076</v>
+        <v>0.1312899960983196</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2252735850168019</v>
+        <v>0.2271735850168019</v>
       </c>
       <c r="C14">
-        <v>13.68907162825218</v>
+        <v>13.36215942244258</v>
       </c>
       <c r="D14">
-        <v>15.53247162825218</v>
+        <v>15.36975942244258</v>
       </c>
       <c r="E14">
-        <v>0.1503999999999996</v>
+        <v>0.3145999999999998</v>
       </c>
       <c r="F14">
-        <v>1.9704</v>
+        <v>2.1346</v>
       </c>
       <c r="G14">
         <v>0.127</v>
@@ -2423,37 +2423,37 @@
         <v>0.061</v>
       </c>
       <c r="M14">
-        <v>0.46462032</v>
+        <v>0.5033386799999999</v>
       </c>
       <c r="N14">
-        <v>-0.40362032</v>
+        <v>-0.4423386799999999</v>
       </c>
       <c r="O14">
-        <v>-0.0686154544</v>
+        <v>-0.0751975756</v>
       </c>
       <c r="P14">
-        <v>-0.3350048656</v>
+        <v>-0.3671411043999999</v>
       </c>
       <c r="Q14">
-        <v>0.1209951344</v>
+        <v>0.0888588956000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2245558317168564</v>
+        <v>0.226610496449234</v>
       </c>
       <c r="T14">
-        <v>0.6401818137588402</v>
+        <v>0.6475402254112406</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.02231929933671433</v>
+        <v>0.02060243015696708</v>
       </c>
       <c r="W14">
-        <v>0.2305371092164028</v>
+        <v>0.2309419469689872</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1312899960983196</v>
+        <v>0.121190765629218</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2271735850168019</v>
+        <v>0.2290735850168019</v>
       </c>
       <c r="C15">
-        <v>13.36215942244258</v>
+        <v>13.03862089638077</v>
       </c>
       <c r="D15">
-        <v>15.36975942244258</v>
+        <v>15.21042089638076</v>
       </c>
       <c r="E15">
-        <v>0.3145999999999998</v>
+        <v>0.4787999999999999</v>
       </c>
       <c r="F15">
-        <v>2.1346</v>
+        <v>2.2988</v>
       </c>
       <c r="G15">
         <v>0.127</v>
@@ -2505,37 +2505,37 @@
         <v>0.061</v>
       </c>
       <c r="M15">
-        <v>0.5033386799999999</v>
+        <v>0.54205704</v>
       </c>
       <c r="N15">
-        <v>-0.4423386799999999</v>
+        <v>-0.48105704</v>
       </c>
       <c r="O15">
-        <v>-0.0751975756</v>
+        <v>-0.08177969680000001</v>
       </c>
       <c r="P15">
-        <v>-0.3671411043999999</v>
+        <v>-0.3992773432</v>
       </c>
       <c r="Q15">
-        <v>0.0888588956000001</v>
+        <v>0.05672265680000005</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.226610496449234</v>
+        <v>0.2287129440823646</v>
       </c>
       <c r="T15">
-        <v>0.6475402254112406</v>
+        <v>0.6550697629160225</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.02060243015696708</v>
+        <v>0.019130828002898</v>
       </c>
       <c r="W15">
-        <v>0.2309419469689872</v>
+        <v>0.2312889507569167</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.121190765629218</v>
+        <v>0.1125342823699882</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2290735850168019</v>
+        <v>0.2309735850168019</v>
       </c>
       <c r="C16">
-        <v>13.03862089638077</v>
+        <v>12.71835220169896</v>
       </c>
       <c r="D16">
-        <v>15.21042089638076</v>
+        <v>15.05435220169895</v>
       </c>
       <c r="E16">
-        <v>0.4787999999999999</v>
+        <v>0.643</v>
       </c>
       <c r="F16">
-        <v>2.2988</v>
+        <v>2.463</v>
       </c>
       <c r="G16">
         <v>0.127</v>
@@ -2587,37 +2587,37 @@
         <v>0.061</v>
       </c>
       <c r="M16">
-        <v>0.54205704</v>
+        <v>0.5807754000000001</v>
       </c>
       <c r="N16">
-        <v>-0.48105704</v>
+        <v>-0.5197754000000001</v>
       </c>
       <c r="O16">
-        <v>-0.08177969680000001</v>
+        <v>-0.08836181800000002</v>
       </c>
       <c r="P16">
-        <v>-0.3992773432</v>
+        <v>-0.4314135820000001</v>
       </c>
       <c r="Q16">
-        <v>0.05672265680000005</v>
+        <v>0.02458641799999994</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2287129440823646</v>
+        <v>0.2308648610715689</v>
       </c>
       <c r="T16">
-        <v>0.6550697629160225</v>
+        <v>0.6627764660091522</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.019130828002898</v>
+        <v>0.01785543946937146</v>
       </c>
       <c r="W16">
-        <v>0.2312889507569167</v>
+        <v>0.2315896873731222</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1125342823699882</v>
+        <v>0.1050319968786556</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2309735850168019</v>
+        <v>0.2328735850168019</v>
       </c>
       <c r="C17">
-        <v>12.71835220169896</v>
+        <v>12.40125370894457</v>
       </c>
       <c r="D17">
-        <v>15.05435220169895</v>
+        <v>14.90145370894457</v>
       </c>
       <c r="E17">
-        <v>0.6429999999999996</v>
+        <v>0.8071999999999997</v>
       </c>
       <c r="F17">
-        <v>2.463</v>
+        <v>2.6272</v>
       </c>
       <c r="G17">
         <v>0.127</v>
@@ -2669,37 +2669,37 @@
         <v>0.061</v>
       </c>
       <c r="M17">
-        <v>0.5807753999999999</v>
+        <v>0.61949376</v>
       </c>
       <c r="N17">
-        <v>-0.5197753999999999</v>
+        <v>-0.55849376</v>
       </c>
       <c r="O17">
-        <v>-0.08836181799999998</v>
+        <v>-0.09494393919999999</v>
       </c>
       <c r="P17">
-        <v>-0.4314135819999999</v>
+        <v>-0.4635498208</v>
       </c>
       <c r="Q17">
-        <v>0.02458641800000011</v>
+        <v>-0.00754982079999994</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2308648610715689</v>
+        <v>0.2330680141795638</v>
       </c>
       <c r="T17">
-        <v>0.6627764660091522</v>
+        <v>0.6706666620330706</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.01785543946937147</v>
+        <v>0.01673947450253575</v>
       </c>
       <c r="W17">
-        <v>0.2315896873731222</v>
+        <v>0.2318528319123021</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1050319968786558</v>
+        <v>0.09846749707373981</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2328735850168019</v>
+        <v>0.2347735850168019</v>
       </c>
       <c r="C18">
-        <v>12.40125370894457</v>
+        <v>12.08722979548875</v>
       </c>
       <c r="D18">
-        <v>14.90145370894457</v>
+        <v>14.75162979548875</v>
       </c>
       <c r="E18">
-        <v>0.8071999999999997</v>
+        <v>0.9713999999999998</v>
       </c>
       <c r="F18">
-        <v>2.6272</v>
+        <v>2.7914</v>
       </c>
       <c r="G18">
         <v>0.127</v>
@@ -2751,37 +2751,37 @@
         <v>0.061</v>
       </c>
       <c r="M18">
-        <v>0.61949376</v>
+        <v>0.65821212</v>
       </c>
       <c r="N18">
-        <v>-0.55849376</v>
+        <v>-0.59721212</v>
       </c>
       <c r="O18">
-        <v>-0.09494393919999999</v>
+        <v>-0.1015260604</v>
       </c>
       <c r="P18">
-        <v>-0.4635498208</v>
+        <v>-0.4956860596</v>
       </c>
       <c r="Q18">
-        <v>-0.00754982079999994</v>
+        <v>-0.03968605959999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2330680141795638</v>
+        <v>0.2353242553142573</v>
       </c>
       <c r="T18">
-        <v>0.6706666620330706</v>
+        <v>0.6787469832623847</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.01673947450253575</v>
+        <v>0.01575479953179836</v>
       </c>
       <c r="W18">
-        <v>0.2318528319123021</v>
+        <v>0.232085018270402</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.09846749707373981</v>
+        <v>0.0926752913635196</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2347735850168019</v>
+        <v>0.2366735850168019</v>
       </c>
       <c r="C19">
-        <v>12.08722979548875</v>
+        <v>11.77618864610204</v>
       </c>
       <c r="D19">
-        <v>14.75162979548875</v>
+        <v>14.60478864610204</v>
       </c>
       <c r="E19">
-        <v>0.9713999999999998</v>
+        <v>1.1356</v>
       </c>
       <c r="F19">
-        <v>2.7914</v>
+        <v>2.9556</v>
       </c>
       <c r="G19">
         <v>0.127</v>
@@ -2833,37 +2833,37 @@
         <v>0.061</v>
       </c>
       <c r="M19">
-        <v>0.65821212</v>
+        <v>0.69693048</v>
       </c>
       <c r="N19">
-        <v>-0.59721212</v>
+        <v>-0.6359304800000001</v>
       </c>
       <c r="O19">
-        <v>-0.1015260604</v>
+        <v>-0.1081081816</v>
       </c>
       <c r="P19">
-        <v>-0.4956860596</v>
+        <v>-0.5278222984000001</v>
       </c>
       <c r="Q19">
-        <v>-0.03968605959999999</v>
+        <v>-0.07182229840000004</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2353242553142573</v>
+        <v>0.2376355267205288</v>
       </c>
       <c r="T19">
-        <v>0.6787469832623847</v>
+        <v>0.6870243854972919</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01575479953179836</v>
+        <v>0.01487953289114289</v>
       </c>
       <c r="W19">
-        <v>0.232085018270402</v>
+        <v>0.2322914061442685</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.0926752913635196</v>
+        <v>0.08752666406554632</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.236673585016802</v>
+        <v>0.238573585016802</v>
       </c>
       <c r="C20">
-        <v>11.77618864610204</v>
+        <v>11.46804206532348</v>
       </c>
       <c r="D20">
-        <v>14.60478864610203</v>
+        <v>14.46084206532347</v>
       </c>
       <c r="E20">
-        <v>1.135599999999999</v>
+        <v>1.2998</v>
       </c>
       <c r="F20">
-        <v>2.9556</v>
+        <v>3.1198</v>
       </c>
       <c r="G20">
         <v>0.127</v>
@@ -2915,37 +2915,37 @@
         <v>0.061</v>
       </c>
       <c r="M20">
-        <v>0.6969304799999999</v>
+        <v>0.73564884</v>
       </c>
       <c r="N20">
-        <v>-0.6359304799999999</v>
+        <v>-0.6746488399999999</v>
       </c>
       <c r="O20">
-        <v>-0.1081081816</v>
+        <v>-0.1146903028</v>
       </c>
       <c r="P20">
-        <v>-0.5278222983999998</v>
+        <v>-0.5599585371999999</v>
       </c>
       <c r="Q20">
-        <v>-0.07182229839999982</v>
+        <v>-0.1039585371999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2376355267205288</v>
+        <v>0.2400038665565847</v>
       </c>
       <c r="T20">
-        <v>0.6870243854972919</v>
+        <v>0.6955061680342954</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.01487953289114289</v>
+        <v>0.01409639958108273</v>
       </c>
       <c r="W20">
-        <v>0.2322914061442685</v>
+        <v>0.2324760689787807</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.08752666406554643</v>
+        <v>0.08291999753578083</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.238573585016802</v>
+        <v>0.2404735850168019</v>
       </c>
       <c r="C21">
-        <v>11.46804206532348</v>
+        <v>11.16270530081717</v>
       </c>
       <c r="D21">
-        <v>14.46084206532347</v>
+        <v>14.31970530081717</v>
       </c>
       <c r="E21">
-        <v>1.2998</v>
+        <v>1.464</v>
       </c>
       <c r="F21">
-        <v>3.1198</v>
+        <v>3.284</v>
       </c>
       <c r="G21">
         <v>0.127</v>
@@ -2997,37 +2997,37 @@
         <v>0.061</v>
       </c>
       <c r="M21">
-        <v>0.73564884</v>
+        <v>0.7743672</v>
       </c>
       <c r="N21">
-        <v>-0.6746488399999999</v>
+        <v>-0.7133672</v>
       </c>
       <c r="O21">
-        <v>-0.1146903028</v>
+        <v>-0.121272424</v>
       </c>
       <c r="P21">
-        <v>-0.5599585371999999</v>
+        <v>-0.5920947759999999</v>
       </c>
       <c r="Q21">
-        <v>-0.1039585371999999</v>
+        <v>-0.1360947759999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2400038665565847</v>
+        <v>0.242431414888542</v>
       </c>
       <c r="T21">
-        <v>0.6955061680342954</v>
+        <v>0.7041999951347241</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.01409639958108273</v>
+        <v>0.0133915796020286</v>
       </c>
       <c r="W21">
-        <v>0.2324760689787807</v>
+        <v>0.2326422655298417</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.08291999753578083</v>
+        <v>0.07877399765899185</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2404735850168019</v>
+        <v>0.242373585016802</v>
       </c>
       <c r="C22">
-        <v>11.16270530081717</v>
+        <v>10.8600968769731</v>
       </c>
       <c r="D22">
-        <v>14.31970530081717</v>
+        <v>14.1812968769731</v>
       </c>
       <c r="E22">
-        <v>1.464</v>
+        <v>1.6282</v>
       </c>
       <c r="F22">
-        <v>3.284</v>
+        <v>3.4482</v>
       </c>
       <c r="G22">
         <v>0.127</v>
@@ -3079,37 +3079,37 @@
         <v>0.061</v>
       </c>
       <c r="M22">
-        <v>0.7743672</v>
+        <v>0.81308556</v>
       </c>
       <c r="N22">
-        <v>-0.7133672</v>
+        <v>-0.75208556</v>
       </c>
       <c r="O22">
-        <v>-0.121272424</v>
+        <v>-0.1278545452</v>
       </c>
       <c r="P22">
-        <v>-0.5920947759999999</v>
+        <v>-0.6242310148000001</v>
       </c>
       <c r="Q22">
-        <v>-0.1360947759999999</v>
+        <v>-0.1682310148000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.242431414888542</v>
+        <v>0.2449204201402957</v>
       </c>
       <c r="T22">
-        <v>0.7041999951347241</v>
+        <v>0.7131139191237713</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.0133915796020286</v>
+        <v>0.01275388533526533</v>
       </c>
       <c r="W22">
-        <v>0.2326422655298417</v>
+        <v>0.2327926338379444</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.07877399765899185</v>
+        <v>0.07502285491332539</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2423735850168019</v>
+        <v>0.2442735850168019</v>
       </c>
       <c r="C23">
-        <v>10.86009687697311</v>
+        <v>10.56013843806564</v>
       </c>
       <c r="D23">
-        <v>14.18129687697311</v>
+        <v>14.04553843806564</v>
       </c>
       <c r="E23">
-        <v>1.628199999999999</v>
+        <v>1.7924</v>
       </c>
       <c r="F23">
-        <v>3.448199999999999</v>
+        <v>3.6124</v>
       </c>
       <c r="G23">
         <v>0.127</v>
@@ -3161,37 +3161,37 @@
         <v>0.061</v>
       </c>
       <c r="M23">
-        <v>0.8130855599999999</v>
+        <v>0.8518039199999999</v>
       </c>
       <c r="N23">
-        <v>-0.7520855599999998</v>
+        <v>-0.7908039199999999</v>
       </c>
       <c r="O23">
-        <v>-0.1278545452</v>
+        <v>-0.1344366664</v>
       </c>
       <c r="P23">
-        <v>-0.6242310147999999</v>
+        <v>-0.6563672535999999</v>
       </c>
       <c r="Q23">
-        <v>-0.1682310147999999</v>
+        <v>-0.2003672535999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2449204201402956</v>
+        <v>0.2474732460395302</v>
       </c>
       <c r="T23">
-        <v>0.7131139191237712</v>
+        <v>0.7222564052663837</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01275388533526533</v>
+        <v>0.01217416327457146</v>
       </c>
       <c r="W23">
-        <v>0.2327926338379444</v>
+        <v>0.2329293322998561</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.07502285491332561</v>
+        <v>0.07161272514453798</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2442735850168019</v>
+        <v>0.2461735850168019</v>
       </c>
       <c r="C24">
-        <v>10.56013843806564</v>
+        <v>10.2627546003353</v>
       </c>
       <c r="D24">
-        <v>14.04553843806564</v>
+        <v>13.9123546003353</v>
       </c>
       <c r="E24">
-        <v>1.7924</v>
+        <v>1.9566</v>
       </c>
       <c r="F24">
-        <v>3.6124</v>
+        <v>3.7766</v>
       </c>
       <c r="G24">
         <v>0.127</v>
@@ -3243,37 +3243,37 @@
         <v>0.061</v>
       </c>
       <c r="M24">
-        <v>0.8518039199999999</v>
+        <v>0.89052228</v>
       </c>
       <c r="N24">
-        <v>-0.7908039199999999</v>
+        <v>-0.8295222799999999</v>
       </c>
       <c r="O24">
-        <v>-0.1344366664</v>
+        <v>-0.1410187876</v>
       </c>
       <c r="P24">
-        <v>-0.6563672535999999</v>
+        <v>-0.6885034924</v>
       </c>
       <c r="Q24">
-        <v>-0.2003672535999999</v>
+        <v>-0.2325034924</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2474732460395302</v>
+        <v>0.2500923791049787</v>
       </c>
       <c r="T24">
-        <v>0.7222564052663837</v>
+        <v>0.7316363585815316</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01217416327457146</v>
+        <v>0.01164485182785096</v>
       </c>
       <c r="W24">
-        <v>0.2329293322998561</v>
+        <v>0.2330541439389928</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.07161272514453798</v>
+        <v>0.06849912839912331</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2461735850168019</v>
+        <v>0.2480735850168019</v>
       </c>
       <c r="C25">
-        <v>10.2627546003353</v>
+        <v>9.96787281240713</v>
       </c>
       <c r="D25">
-        <v>13.9123546003353</v>
+        <v>13.78167281240713</v>
       </c>
       <c r="E25">
-        <v>1.9566</v>
+        <v>2.1208</v>
       </c>
       <c r="F25">
-        <v>3.7766</v>
+        <v>3.9408</v>
       </c>
       <c r="G25">
         <v>0.127</v>
@@ -3325,37 +3325,37 @@
         <v>0.061</v>
       </c>
       <c r="M25">
-        <v>0.89052228</v>
+        <v>0.92924064</v>
       </c>
       <c r="N25">
-        <v>-0.8295222799999999</v>
+        <v>-0.86824064</v>
       </c>
       <c r="O25">
-        <v>-0.1410187876</v>
+        <v>-0.1476009088</v>
       </c>
       <c r="P25">
-        <v>-0.6885034924</v>
+        <v>-0.7206397312</v>
       </c>
       <c r="Q25">
-        <v>-0.2325034924</v>
+        <v>-0.2646397312</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2500923791049787</v>
+        <v>0.252780436724781</v>
       </c>
       <c r="T25">
-        <v>0.7316363585815316</v>
+        <v>0.7412631527733938</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01164485182785096</v>
+        <v>0.01115964966835717</v>
       </c>
       <c r="W25">
-        <v>0.2330541439389928</v>
+        <v>0.2331685546082014</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.06849912839912331</v>
+        <v>0.06564499804915969</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2480735850168019</v>
+        <v>0.2499735850168019</v>
       </c>
       <c r="C26">
-        <v>9.96787281240713</v>
+        <v>9.675423223502577</v>
       </c>
       <c r="D26">
-        <v>13.78167281240713</v>
+        <v>13.65342322350257</v>
       </c>
       <c r="E26">
-        <v>2.120799999999999</v>
+        <v>2.284999999999999</v>
       </c>
       <c r="F26">
-        <v>3.940799999999999</v>
+        <v>4.105</v>
       </c>
       <c r="G26">
         <v>0.127</v>
@@ -3407,37 +3407,37 @@
         <v>0.061</v>
       </c>
       <c r="M26">
-        <v>0.92924064</v>
+        <v>0.9679589999999999</v>
       </c>
       <c r="N26">
-        <v>-0.86824064</v>
+        <v>-0.9069589999999998</v>
       </c>
       <c r="O26">
-        <v>-0.1476009088</v>
+        <v>-0.15418303</v>
       </c>
       <c r="P26">
-        <v>-0.7206397312</v>
+        <v>-0.7527759699999998</v>
       </c>
       <c r="Q26">
-        <v>-0.2646397312</v>
+        <v>-0.2967759699999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.252780436724781</v>
+        <v>0.2555401758811114</v>
       </c>
       <c r="T26">
-        <v>0.7412631527733938</v>
+        <v>0.7511466614770391</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01115964966835717</v>
+        <v>0.01071326368162288</v>
       </c>
       <c r="W26">
-        <v>0.2331685546082014</v>
+        <v>0.2332738124238734</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.06564499804915969</v>
+        <v>0.06301919812719348</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2499735850168019</v>
+        <v>0.2518735850168019</v>
       </c>
       <c r="C27">
-        <v>9.675423223502577</v>
+        <v>9.385338558941907</v>
       </c>
       <c r="D27">
-        <v>13.65342322350257</v>
+        <v>13.52753855894191</v>
       </c>
       <c r="E27">
-        <v>2.284999999999999</v>
+        <v>2.449199999999999</v>
       </c>
       <c r="F27">
-        <v>4.105</v>
+        <v>4.2692</v>
       </c>
       <c r="G27">
         <v>0.127</v>
@@ -3489,37 +3489,37 @@
         <v>0.061</v>
       </c>
       <c r="M27">
-        <v>0.9679589999999999</v>
+        <v>1.00667736</v>
       </c>
       <c r="N27">
-        <v>-0.9069589999999998</v>
+        <v>-0.9456773599999999</v>
       </c>
       <c r="O27">
-        <v>-0.15418303</v>
+        <v>-0.1607651512</v>
       </c>
       <c r="P27">
-        <v>-0.7527759699999998</v>
+        <v>-0.7849122087999999</v>
       </c>
       <c r="Q27">
-        <v>-0.2967759699999998</v>
+        <v>-0.3289122087999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2555401758811114</v>
+        <v>0.2583745025822076</v>
       </c>
       <c r="T27">
-        <v>0.7511466614770391</v>
+        <v>0.7612972920375397</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.01071326368162288</v>
+        <v>0.01030121507848354</v>
       </c>
       <c r="W27">
-        <v>0.2332738124238734</v>
+        <v>0.2333709734844936</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.06301919812719348</v>
+        <v>0.06059538281460897</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2518735850168019</v>
+        <v>0.2537735850168019</v>
       </c>
       <c r="C28">
-        <v>9.385338558941907</v>
+        <v>9.097554002470883</v>
       </c>
       <c r="D28">
-        <v>13.52753855894191</v>
+        <v>13.40395400247088</v>
       </c>
       <c r="E28">
-        <v>2.449199999999999</v>
+        <v>2.6134</v>
       </c>
       <c r="F28">
-        <v>4.2692</v>
+        <v>4.4334</v>
       </c>
       <c r="G28">
         <v>0.127</v>
@@ -3571,37 +3571,37 @@
         <v>0.061</v>
       </c>
       <c r="M28">
-        <v>1.00667736</v>
+        <v>1.04539572</v>
       </c>
       <c r="N28">
-        <v>-0.9456773599999999</v>
+        <v>-0.98439572</v>
       </c>
       <c r="O28">
-        <v>-0.1607651512</v>
+        <v>-0.1673472724</v>
       </c>
       <c r="P28">
-        <v>-0.7849122087999999</v>
+        <v>-0.8170484475999999</v>
       </c>
       <c r="Q28">
-        <v>-0.3289122087999999</v>
+        <v>-0.3610484475999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2583745025822076</v>
+        <v>0.261286482069635</v>
       </c>
       <c r="T28">
-        <v>0.7612972920375397</v>
+        <v>0.771726022065451</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01030121507848354</v>
+        <v>0.009919688594095259</v>
       </c>
       <c r="W28">
-        <v>0.2333709734844936</v>
+        <v>0.2334609374295123</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.06059538281460897</v>
+        <v>0.05835110937703092</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2537735850168019</v>
+        <v>0.2556735850168019</v>
       </c>
       <c r="C29">
-        <v>9.097554002470883</v>
+        <v>8.812007084979308</v>
       </c>
       <c r="D29">
-        <v>13.40395400247088</v>
+        <v>13.28260708497931</v>
       </c>
       <c r="E29">
-        <v>2.6134</v>
+        <v>2.7776</v>
       </c>
       <c r="F29">
-        <v>4.4334</v>
+        <v>4.5976</v>
       </c>
       <c r="G29">
         <v>0.127</v>
@@ -3653,37 +3653,37 @@
         <v>0.061</v>
       </c>
       <c r="M29">
-        <v>1.04539572</v>
+        <v>1.08411408</v>
       </c>
       <c r="N29">
-        <v>-0.98439572</v>
+        <v>-1.02311408</v>
       </c>
       <c r="O29">
-        <v>-0.1673472724</v>
+        <v>-0.1739293936</v>
       </c>
       <c r="P29">
-        <v>-0.8170484475999999</v>
+        <v>-0.8491846864</v>
       </c>
       <c r="Q29">
-        <v>-0.3610484475999999</v>
+        <v>-0.3931846864</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.261286482069635</v>
+        <v>0.2642793498761578</v>
       </c>
       <c r="T29">
-        <v>0.771726022065451</v>
+        <v>0.7824444390385824</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.009919688594095259</v>
+        <v>0.009565414001449</v>
       </c>
       <c r="W29">
-        <v>0.2334609374295123</v>
+        <v>0.2335444753784583</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.05835110937703092</v>
+        <v>0.0562671411849941</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2556735850168019</v>
+        <v>0.2575735850168019</v>
       </c>
       <c r="C30">
-        <v>8.812007084979308</v>
+        <v>8.528637579209938</v>
       </c>
       <c r="D30">
-        <v>13.28260708497931</v>
+        <v>13.16343757920994</v>
       </c>
       <c r="E30">
-        <v>2.7776</v>
+        <v>2.9418</v>
       </c>
       <c r="F30">
-        <v>4.5976</v>
+        <v>4.7618</v>
       </c>
       <c r="G30">
         <v>0.127</v>
@@ -3735,37 +3735,37 @@
         <v>0.061</v>
       </c>
       <c r="M30">
-        <v>1.08411408</v>
+        <v>1.12283244</v>
       </c>
       <c r="N30">
-        <v>-1.02311408</v>
+        <v>-1.06183244</v>
       </c>
       <c r="O30">
-        <v>-0.1739293936</v>
+        <v>-0.1805115148</v>
       </c>
       <c r="P30">
-        <v>-0.8491846864</v>
+        <v>-0.8813209252</v>
       </c>
       <c r="Q30">
-        <v>-0.3931846864</v>
+        <v>-0.4253209252</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2642793498761578</v>
+        <v>0.2673565238180755</v>
       </c>
       <c r="T30">
-        <v>0.7824444390385824</v>
+        <v>0.7934647832503934</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.009565414001449</v>
+        <v>0.009235572139330069</v>
       </c>
       <c r="W30">
-        <v>0.2335444753784583</v>
+        <v>0.233622252089546</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.0562671411849941</v>
+        <v>0.05432689493723564</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2575735850168019</v>
+        <v>0.2594735850168019</v>
       </c>
       <c r="C31">
-        <v>8.52863757920994</v>
+        <v>8.247387400084932</v>
       </c>
       <c r="D31">
-        <v>13.16343757920994</v>
+        <v>13.04638740008493</v>
       </c>
       <c r="E31">
-        <v>2.941799999999999</v>
+        <v>3.105999999999999</v>
       </c>
       <c r="F31">
-        <v>4.761799999999999</v>
+        <v>4.925999999999999</v>
       </c>
       <c r="G31">
         <v>0.127</v>
@@ -3817,37 +3817,37 @@
         <v>0.061</v>
       </c>
       <c r="M31">
-        <v>1.12283244</v>
+        <v>1.1615508</v>
       </c>
       <c r="N31">
-        <v>-1.06183244</v>
+        <v>-1.1005508</v>
       </c>
       <c r="O31">
-        <v>-0.1805115148</v>
+        <v>-0.187093636</v>
       </c>
       <c r="P31">
-        <v>-0.8813209251999998</v>
+        <v>-0.913457164</v>
       </c>
       <c r="Q31">
-        <v>-0.4253209251999998</v>
+        <v>-0.457457164</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2673565238180755</v>
+        <v>0.2705216170154766</v>
       </c>
       <c r="T31">
-        <v>0.7934647832503934</v>
+        <v>0.8047999944396848</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.009235572139330069</v>
+        <v>0.008927719734685733</v>
       </c>
       <c r="W31">
-        <v>0.233622252089546</v>
+        <v>0.2336948436865611</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.05432689493723564</v>
+        <v>0.05251599843932775</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2594735850168019</v>
+        <v>0.2613735850168019</v>
       </c>
       <c r="C32">
-        <v>8.247387400084932</v>
+        <v>7.968200510303287</v>
       </c>
       <c r="D32">
-        <v>13.04638740008493</v>
+        <v>12.93140051030329</v>
       </c>
       <c r="E32">
-        <v>3.105999999999999</v>
+        <v>3.270199999999999</v>
       </c>
       <c r="F32">
-        <v>4.925999999999999</v>
+        <v>5.090199999999999</v>
       </c>
       <c r="G32">
         <v>0.127</v>
@@ -3899,37 +3899,37 @@
         <v>0.061</v>
       </c>
       <c r="M32">
-        <v>1.1615508</v>
+        <v>1.20026916</v>
       </c>
       <c r="N32">
-        <v>-1.1005508</v>
+        <v>-1.13926916</v>
       </c>
       <c r="O32">
-        <v>-0.187093636</v>
+        <v>-0.1936757572</v>
       </c>
       <c r="P32">
-        <v>-0.913457164</v>
+        <v>-0.9455934027999999</v>
       </c>
       <c r="Q32">
-        <v>-0.457457164</v>
+        <v>-0.4895934027999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2705216170154766</v>
+        <v>0.2737784520446863</v>
       </c>
       <c r="T32">
-        <v>0.8047999944396848</v>
+        <v>0.8164637624750425</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.008927719734685733</v>
+        <v>0.008639728775502323</v>
       </c>
       <c r="W32">
-        <v>0.2336948436865611</v>
+        <v>0.2337627519547366</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.05251599843932775</v>
+        <v>0.05082193397354307</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2613735850168019</v>
+        <v>0.2632735850168019</v>
       </c>
       <c r="C33">
-        <v>7.968200510303287</v>
+        <v>7.691022830886829</v>
       </c>
       <c r="D33">
-        <v>12.93140051030329</v>
+        <v>12.81842283088683</v>
       </c>
       <c r="E33">
-        <v>3.270199999999999</v>
+        <v>3.434399999999999</v>
       </c>
       <c r="F33">
-        <v>5.090199999999999</v>
+        <v>5.2544</v>
       </c>
       <c r="G33">
         <v>0.127</v>
@@ -3981,37 +3981,37 @@
         <v>0.061</v>
       </c>
       <c r="M33">
-        <v>1.20026916</v>
+        <v>1.23898752</v>
       </c>
       <c r="N33">
-        <v>-1.13926916</v>
+        <v>-1.17798752</v>
       </c>
       <c r="O33">
-        <v>-0.1936757572</v>
+        <v>-0.2002578784</v>
       </c>
       <c r="P33">
-        <v>-0.9455934027999999</v>
+        <v>-0.9777296416000001</v>
       </c>
       <c r="Q33">
-        <v>-0.4895934027999999</v>
+        <v>-0.5217296416000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2737784520446863</v>
+        <v>0.2771310763394612</v>
       </c>
       <c r="T33">
-        <v>0.8164637624750425</v>
+        <v>0.8284705825114402</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.008639728775502323</v>
+        <v>0.008369737251267875</v>
       </c>
       <c r="W33">
-        <v>0.2337627519547366</v>
+        <v>0.233826415956151</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.05082193397354307</v>
+        <v>0.04923374853686979</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2632735850168019</v>
+        <v>0.2651735850168019</v>
       </c>
       <c r="C34">
-        <v>7.691022830886829</v>
+        <v>7.415802156374806</v>
       </c>
       <c r="D34">
-        <v>12.81842283088683</v>
+        <v>12.7074021563748</v>
       </c>
       <c r="E34">
-        <v>3.434399999999999</v>
+        <v>3.598599999999999</v>
       </c>
       <c r="F34">
-        <v>5.2544</v>
+        <v>5.4186</v>
       </c>
       <c r="G34">
         <v>0.127</v>
@@ -4063,37 +4063,37 @@
         <v>0.061</v>
       </c>
       <c r="M34">
-        <v>1.23898752</v>
+        <v>1.27770588</v>
       </c>
       <c r="N34">
-        <v>-1.17798752</v>
+        <v>-1.21670588</v>
       </c>
       <c r="O34">
-        <v>-0.2002578784</v>
+        <v>-0.2068399996</v>
       </c>
       <c r="P34">
-        <v>-0.9777296416000001</v>
+        <v>-1.0098658804</v>
       </c>
       <c r="Q34">
-        <v>-0.5217296416000001</v>
+        <v>-0.5538658804000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2771310763394612</v>
+        <v>0.2805837789713934</v>
       </c>
       <c r="T34">
-        <v>0.8284705825114402</v>
+        <v>0.8408358150862378</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.008369737251267875</v>
+        <v>0.008116108849714303</v>
       </c>
       <c r="W34">
-        <v>0.233826415956151</v>
+        <v>0.2338862215332374</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.04923374853686979</v>
+        <v>0.04774181676302525</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2651735850168019</v>
+        <v>0.2670735850168019</v>
       </c>
       <c r="C35">
-        <v>7.415802156374806</v>
+        <v>7.142488074387667</v>
       </c>
       <c r="D35">
-        <v>12.7074021563748</v>
+        <v>12.59828807438767</v>
       </c>
       <c r="E35">
-        <v>3.598599999999999</v>
+        <v>3.762799999999999</v>
       </c>
       <c r="F35">
-        <v>5.4186</v>
+        <v>5.5828</v>
       </c>
       <c r="G35">
         <v>0.127</v>
@@ -4145,37 +4145,37 @@
         <v>0.061</v>
       </c>
       <c r="M35">
-        <v>1.27770588</v>
+        <v>1.31642424</v>
       </c>
       <c r="N35">
-        <v>-1.21670588</v>
+        <v>-1.25542424</v>
       </c>
       <c r="O35">
-        <v>-0.2068399996</v>
+        <v>-0.2134221208</v>
       </c>
       <c r="P35">
-        <v>-1.0098658804</v>
+        <v>-1.0420021192</v>
       </c>
       <c r="Q35">
-        <v>-0.5538658804000001</v>
+        <v>-0.5860021192</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2805837789713934</v>
+        <v>0.2841411089558084</v>
       </c>
       <c r="T35">
-        <v>0.8408358150862378</v>
+        <v>0.8535757516784535</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.008116108849714303</v>
+        <v>0.007877399765899178</v>
       </c>
       <c r="W35">
-        <v>0.2338862215332374</v>
+        <v>0.233942509135201</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.04774181676302525</v>
+        <v>0.0463376456817598</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2670735850168019</v>
+        <v>0.2689735850168019</v>
       </c>
       <c r="C36">
-        <v>7.142488074387667</v>
+        <v>6.871031889299566</v>
       </c>
       <c r="D36">
-        <v>12.59828807438767</v>
+        <v>12.49103188929957</v>
       </c>
       <c r="E36">
-        <v>3.762799999999999</v>
+        <v>3.927</v>
       </c>
       <c r="F36">
-        <v>5.5828</v>
+        <v>5.747</v>
       </c>
       <c r="G36">
         <v>0.127</v>
@@ -4227,37 +4227,37 @@
         <v>0.061</v>
       </c>
       <c r="M36">
-        <v>1.31642424</v>
+        <v>1.3551426</v>
       </c>
       <c r="N36">
-        <v>-1.25542424</v>
+        <v>-1.2941426</v>
       </c>
       <c r="O36">
-        <v>-0.2134221208</v>
+        <v>-0.220004242</v>
       </c>
       <c r="P36">
-        <v>-1.0420021192</v>
+        <v>-1.074138358</v>
       </c>
       <c r="Q36">
-        <v>-0.5860021192</v>
+        <v>-0.6181383579999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2841411089558084</v>
+        <v>0.2878078952474363</v>
       </c>
       <c r="T36">
-        <v>0.8535757516784535</v>
+        <v>0.8667076863196606</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.007877399765899178</v>
+        <v>0.0076523312011592</v>
       </c>
       <c r="W36">
-        <v>0.233942509135201</v>
+        <v>0.2339955803027667</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.0463376456817598</v>
+        <v>0.04501371294799528</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2689735850168019</v>
+        <v>0.2708735850168019</v>
       </c>
       <c r="C37">
-        <v>6.871031889299566</v>
+        <v>6.601386549776952</v>
       </c>
       <c r="D37">
-        <v>12.49103188929957</v>
+        <v>12.38558654977695</v>
       </c>
       <c r="E37">
-        <v>3.927</v>
+        <v>4.0912</v>
       </c>
       <c r="F37">
-        <v>5.747</v>
+        <v>5.9112</v>
       </c>
       <c r="G37">
         <v>0.127</v>
@@ -4309,37 +4309,37 @@
         <v>0.061</v>
       </c>
       <c r="M37">
-        <v>1.3551426</v>
+        <v>1.39386096</v>
       </c>
       <c r="N37">
-        <v>-1.2941426</v>
+        <v>-1.33286096</v>
       </c>
       <c r="O37">
-        <v>-0.220004242</v>
+        <v>-0.2265863632</v>
       </c>
       <c r="P37">
-        <v>-1.074138358</v>
+        <v>-1.1062745968</v>
       </c>
       <c r="Q37">
-        <v>-0.6181383579999999</v>
+        <v>-0.6502745968000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2878078952474363</v>
+        <v>0.2915892686106775</v>
       </c>
       <c r="T37">
-        <v>0.8667076863196606</v>
+        <v>0.8802499939184053</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0076523312011592</v>
+        <v>0.007439766445571444</v>
       </c>
       <c r="W37">
-        <v>0.2339955803027667</v>
+        <v>0.2340457030721343</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.04501371294799528</v>
+        <v>0.04376333203277316</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2708735850168019</v>
+        <v>0.2727735850168019</v>
       </c>
       <c r="C38">
-        <v>6.601386549776953</v>
+        <v>6.333506579956523</v>
       </c>
       <c r="D38">
-        <v>12.38558654977695</v>
+        <v>12.28190657995652</v>
       </c>
       <c r="E38">
-        <v>4.091199999999999</v>
+        <v>4.255399999999999</v>
       </c>
       <c r="F38">
-        <v>5.911199999999999</v>
+        <v>6.075399999999999</v>
       </c>
       <c r="G38">
         <v>0.127</v>
@@ -4391,37 +4391,37 @@
         <v>0.061</v>
       </c>
       <c r="M38">
-        <v>1.39386096</v>
+        <v>1.43257932</v>
       </c>
       <c r="N38">
-        <v>-1.33286096</v>
+        <v>-1.37157932</v>
       </c>
       <c r="O38">
-        <v>-0.2265863632</v>
+        <v>-0.2331684844</v>
       </c>
       <c r="P38">
-        <v>-1.1062745968</v>
+        <v>-1.1384108356</v>
       </c>
       <c r="Q38">
-        <v>-0.6502745967999999</v>
+        <v>-0.6824108356</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2915892686106774</v>
+        <v>0.2954906855727517</v>
       </c>
       <c r="T38">
-        <v>0.8802499939184051</v>
+        <v>0.8942222160440941</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.007439766445571445</v>
+        <v>0.007238691676772217</v>
       </c>
       <c r="W38">
-        <v>0.2340457030721343</v>
+        <v>0.2340931165026171</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.04376333203277316</v>
+        <v>0.04258053927513061</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2727735850168019</v>
+        <v>0.2746735850168019</v>
       </c>
       <c r="C39">
-        <v>6.333506579956523</v>
+        <v>6.067348014051223</v>
       </c>
       <c r="D39">
-        <v>12.28190657995652</v>
+        <v>12.17994801405122</v>
       </c>
       <c r="E39">
-        <v>4.255399999999999</v>
+        <v>4.419599999999999</v>
       </c>
       <c r="F39">
-        <v>6.075399999999999</v>
+        <v>6.239599999999999</v>
       </c>
       <c r="G39">
         <v>0.127</v>
@@ -4473,37 +4473,37 @@
         <v>0.061</v>
       </c>
       <c r="M39">
-        <v>1.43257932</v>
+        <v>1.47129768</v>
       </c>
       <c r="N39">
-        <v>-1.37157932</v>
+        <v>-1.41029768</v>
       </c>
       <c r="O39">
-        <v>-0.2331684844</v>
+        <v>-0.2397506056</v>
       </c>
       <c r="P39">
-        <v>-1.1384108356</v>
+        <v>-1.1705470744</v>
       </c>
       <c r="Q39">
-        <v>-0.6824108356</v>
+        <v>-0.7145470744</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2954906855727517</v>
+        <v>0.2995179546948929</v>
       </c>
       <c r="T39">
-        <v>0.8942222160440941</v>
+        <v>0.9086451550125473</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.007238691676772217</v>
+        <v>0.007048199790541367</v>
       </c>
       <c r="W39">
-        <v>0.2340931165026171</v>
+        <v>0.2341380344893904</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.04258053927513061</v>
+        <v>0.0414599987678903</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2746735850168019</v>
+        <v>0.2765735850168019</v>
       </c>
       <c r="C40">
-        <v>6.067348014051223</v>
+        <v>5.802868334186598</v>
       </c>
       <c r="D40">
-        <v>12.17994801405122</v>
+        <v>12.0796683341866</v>
       </c>
       <c r="E40">
-        <v>4.419599999999999</v>
+        <v>4.583799999999999</v>
       </c>
       <c r="F40">
-        <v>6.239599999999999</v>
+        <v>6.403799999999999</v>
       </c>
       <c r="G40">
         <v>0.127</v>
@@ -4555,37 +4555,37 @@
         <v>0.061</v>
       </c>
       <c r="M40">
-        <v>1.47129768</v>
+        <v>1.51001604</v>
       </c>
       <c r="N40">
-        <v>-1.41029768</v>
+        <v>-1.44901604</v>
       </c>
       <c r="O40">
-        <v>-0.2397506056</v>
+        <v>-0.2463327268</v>
       </c>
       <c r="P40">
-        <v>-1.1705470744</v>
+        <v>-1.2026833132</v>
       </c>
       <c r="Q40">
-        <v>-0.7145470744</v>
+        <v>-0.7466833132000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2995179546948929</v>
+        <v>0.303677265427596</v>
       </c>
       <c r="T40">
-        <v>0.9086451550125473</v>
+        <v>0.9235409772258678</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.007048199790541367</v>
+        <v>0.006867476718989025</v>
       </c>
       <c r="W40">
-        <v>0.2341380344893904</v>
+        <v>0.2341806489896624</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.0414599987678903</v>
+        <v>0.04039692187640598</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2765735850168019</v>
+        <v>0.278473585016802</v>
       </c>
       <c r="C41">
-        <v>5.802868334186598</v>
+        <v>5.540026411282895</v>
       </c>
       <c r="D41">
-        <v>12.0796683341866</v>
+        <v>11.98102641128289</v>
       </c>
       <c r="E41">
-        <v>4.583799999999999</v>
+        <v>4.747999999999999</v>
       </c>
       <c r="F41">
-        <v>6.403799999999999</v>
+        <v>6.568</v>
       </c>
       <c r="G41">
         <v>0.127</v>
@@ -4637,37 +4637,37 @@
         <v>0.061</v>
       </c>
       <c r="M41">
-        <v>1.51001604</v>
+        <v>1.5487344</v>
       </c>
       <c r="N41">
-        <v>-1.44901604</v>
+        <v>-1.4877344</v>
       </c>
       <c r="O41">
-        <v>-0.2463327268</v>
+        <v>-0.252914848</v>
       </c>
       <c r="P41">
-        <v>-1.2026833132</v>
+        <v>-1.234819552</v>
       </c>
       <c r="Q41">
-        <v>-0.7466833132000001</v>
+        <v>-0.7788195520000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.303677265427596</v>
+        <v>0.3079752198513893</v>
       </c>
       <c r="T41">
-        <v>0.9235409772258678</v>
+        <v>0.9389333268462989</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.006867476718989025</v>
+        <v>0.006695789801014299</v>
       </c>
       <c r="W41">
-        <v>0.2341806489896624</v>
+        <v>0.2342211327649208</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.04039692187640598</v>
+        <v>0.03938699882949581</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.278473585016802</v>
+        <v>0.2803735850168019</v>
       </c>
       <c r="C42">
-        <v>5.540026411282895</v>
+        <v>5.278782448810282</v>
       </c>
       <c r="D42">
-        <v>11.98102641128289</v>
+        <v>11.88398244881028</v>
       </c>
       <c r="E42">
-        <v>4.747999999999999</v>
+        <v>4.912199999999999</v>
       </c>
       <c r="F42">
-        <v>6.568</v>
+        <v>6.7322</v>
       </c>
       <c r="G42">
         <v>0.127</v>
@@ -4719,37 +4719,37 @@
         <v>0.061</v>
       </c>
       <c r="M42">
-        <v>1.5487344</v>
+        <v>1.58745276</v>
       </c>
       <c r="N42">
-        <v>-1.4877344</v>
+        <v>-1.52645276</v>
       </c>
       <c r="O42">
-        <v>-0.252914848</v>
+        <v>-0.2594969692</v>
       </c>
       <c r="P42">
-        <v>-1.234819552</v>
+        <v>-1.2669557908</v>
       </c>
       <c r="Q42">
-        <v>-0.7788195520000001</v>
+        <v>-0.8109557908</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3079752198513893</v>
+        <v>0.3124188676454807</v>
       </c>
       <c r="T42">
-        <v>0.9389333268462989</v>
+        <v>0.9548474510301345</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.006695789801014299</v>
+        <v>0.006532477854648098</v>
       </c>
       <c r="W42">
-        <v>0.2342211327649208</v>
+        <v>0.234259641721874</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.03938699882949581</v>
+        <v>0.03842634032145931</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2803735850168019</v>
+        <v>0.2822735850168019</v>
       </c>
       <c r="C43">
-        <v>5.278782448810282</v>
+        <v>5.019097929255446</v>
       </c>
       <c r="D43">
-        <v>11.88398244881028</v>
+        <v>11.78849792925545</v>
       </c>
       <c r="E43">
-        <v>4.912199999999999</v>
+        <v>5.0764</v>
       </c>
       <c r="F43">
-        <v>6.7322</v>
+        <v>6.8964</v>
       </c>
       <c r="G43">
         <v>0.127</v>
@@ -4801,37 +4801,37 @@
         <v>0.061</v>
       </c>
       <c r="M43">
-        <v>1.58745276</v>
+        <v>1.62617112</v>
       </c>
       <c r="N43">
-        <v>-1.52645276</v>
+        <v>-1.56517112</v>
       </c>
       <c r="O43">
-        <v>-0.2594969692</v>
+        <v>-0.2660790904000001</v>
       </c>
       <c r="P43">
-        <v>-1.2669557908</v>
+        <v>-1.2990920296</v>
       </c>
       <c r="Q43">
-        <v>-0.8109557908</v>
+        <v>-0.8430920296</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3124188676454807</v>
+        <v>0.317015744673851</v>
       </c>
       <c r="T43">
-        <v>0.9548474510301345</v>
+        <v>0.971310338116861</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.006532477854648098</v>
+        <v>0.006376942667632667</v>
       </c>
       <c r="W43">
-        <v>0.234259641721874</v>
+        <v>0.2342963169189722</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.03842634032145931</v>
+        <v>0.03751142745666269</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2822735850168019</v>
+        <v>0.284173585016802</v>
       </c>
       <c r="C44">
-        <v>5.019097929255445</v>
+        <v>4.760935563148449</v>
       </c>
       <c r="D44">
-        <v>11.78849792925544</v>
+        <v>11.69453556314845</v>
       </c>
       <c r="E44">
-        <v>5.076399999999999</v>
+        <v>5.240599999999999</v>
       </c>
       <c r="F44">
-        <v>6.896399999999999</v>
+        <v>7.060599999999999</v>
       </c>
       <c r="G44">
         <v>0.127</v>
@@ -4883,37 +4883,37 @@
         <v>0.061</v>
       </c>
       <c r="M44">
-        <v>1.62617112</v>
+        <v>1.66488948</v>
       </c>
       <c r="N44">
-        <v>-1.56517112</v>
+        <v>-1.60388948</v>
       </c>
       <c r="O44">
-        <v>-0.2660790904</v>
+        <v>-0.2726612116</v>
       </c>
       <c r="P44">
-        <v>-1.2990920296</v>
+        <v>-1.3312282684</v>
       </c>
       <c r="Q44">
-        <v>-0.8430920295999997</v>
+        <v>-0.8752282683999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.317015744673851</v>
+        <v>0.3217739156330414</v>
       </c>
       <c r="T44">
-        <v>0.9713103381168608</v>
+        <v>0.9883508703645251</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.006376942667632667</v>
+        <v>0.00622864167536214</v>
       </c>
       <c r="W44">
-        <v>0.2342963169189722</v>
+        <v>0.2343312862929496</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.03751142745666269</v>
+        <v>0.03663906867860078</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.284173585016802</v>
+        <v>0.2860735850168019</v>
       </c>
       <c r="C45">
-        <v>4.760935563148449</v>
+        <v>4.50425924050804</v>
       </c>
       <c r="D45">
-        <v>11.69453556314845</v>
+        <v>11.60205924050804</v>
       </c>
       <c r="E45">
-        <v>5.240599999999999</v>
+        <v>5.404799999999999</v>
       </c>
       <c r="F45">
-        <v>7.060599999999999</v>
+        <v>7.224799999999999</v>
       </c>
       <c r="G45">
         <v>0.127</v>
@@ -4965,37 +4965,37 @@
         <v>0.061</v>
       </c>
       <c r="M45">
-        <v>1.66488948</v>
+        <v>1.70360784</v>
       </c>
       <c r="N45">
-        <v>-1.60388948</v>
+        <v>-1.64260784</v>
       </c>
       <c r="O45">
-        <v>-0.2726612116</v>
+        <v>-0.2792433328</v>
       </c>
       <c r="P45">
-        <v>-1.3312282684</v>
+        <v>-1.3633645072</v>
       </c>
       <c r="Q45">
-        <v>-0.8752282683999999</v>
+        <v>-0.9073645072000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3217739156330414</v>
+        <v>0.3267020212693457</v>
       </c>
       <c r="T45">
-        <v>0.9883508703645251</v>
+        <v>1.005999993049606</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.00622864167536214</v>
+        <v>0.006087081637285728</v>
       </c>
       <c r="W45">
-        <v>0.2343312862929496</v>
+        <v>0.234364666149928</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.03663906867860078</v>
+        <v>0.03580636257226899</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2860735850168019</v>
+        <v>0.2879735850168019</v>
       </c>
       <c r="C46">
-        <v>4.50425924050804</v>
+        <v>4.249033984572566</v>
       </c>
       <c r="D46">
-        <v>11.60205924050804</v>
+        <v>11.51103398457257</v>
       </c>
       <c r="E46">
-        <v>5.404799999999999</v>
+        <v>5.568999999999999</v>
       </c>
       <c r="F46">
-        <v>7.224799999999999</v>
+        <v>7.388999999999999</v>
       </c>
       <c r="G46">
         <v>0.127</v>
@@ -5047,37 +5047,37 @@
         <v>0.061</v>
       </c>
       <c r="M46">
-        <v>1.70360784</v>
+        <v>1.7423262</v>
       </c>
       <c r="N46">
-        <v>-1.64260784</v>
+        <v>-1.6813262</v>
       </c>
       <c r="O46">
-        <v>-0.2792433328</v>
+        <v>-0.285825454</v>
       </c>
       <c r="P46">
-        <v>-1.3633645072</v>
+        <v>-1.395500746</v>
       </c>
       <c r="Q46">
-        <v>-0.9073645072000001</v>
+        <v>-0.939500746</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3267020212693457</v>
+        <v>0.3318093307469702</v>
       </c>
       <c r="T46">
-        <v>1.005999993049606</v>
+        <v>1.024290902014144</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.006087081637285728</v>
+        <v>0.005951813156457156</v>
       </c>
       <c r="W46">
-        <v>0.234364666149928</v>
+        <v>0.2343965624577074</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.03580636257226899</v>
+        <v>0.03501066562621857</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2879735850168019</v>
+        <v>0.2898735850168019</v>
       </c>
       <c r="C47">
-        <v>4.249033984572566</v>
+        <v>3.995225907692055</v>
       </c>
       <c r="D47">
-        <v>11.51103398457257</v>
+        <v>11.42142590769205</v>
       </c>
       <c r="E47">
-        <v>5.568999999999999</v>
+        <v>5.733199999999999</v>
       </c>
       <c r="F47">
-        <v>7.388999999999999</v>
+        <v>7.553199999999999</v>
       </c>
       <c r="G47">
         <v>0.127</v>
@@ -5129,37 +5129,37 @@
         <v>0.061</v>
       </c>
       <c r="M47">
-        <v>1.7423262</v>
+        <v>1.78104456</v>
       </c>
       <c r="N47">
-        <v>-1.6813262</v>
+        <v>-1.72004456</v>
       </c>
       <c r="O47">
-        <v>-0.285825454</v>
+        <v>-0.2924075752</v>
       </c>
       <c r="P47">
-        <v>-1.395500746</v>
+        <v>-1.4276369848</v>
       </c>
       <c r="Q47">
-        <v>-0.939500746</v>
+        <v>-0.9716369847999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3318093307469702</v>
+        <v>0.337105799834877</v>
       </c>
       <c r="T47">
-        <v>1.024290902014144</v>
+        <v>1.043259252051443</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.005951813156457156</v>
+        <v>0.005822425913925478</v>
       </c>
       <c r="W47">
-        <v>0.2343965624577074</v>
+        <v>0.2344270719694964</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.03501066562621857</v>
+        <v>0.0342495641995616</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2898735850168019</v>
+        <v>0.291773585016802</v>
       </c>
       <c r="C48">
-        <v>3.995225907692055</v>
+        <v>3.742802169264479</v>
       </c>
       <c r="D48">
-        <v>11.42142590769205</v>
+        <v>11.33320216926448</v>
       </c>
       <c r="E48">
-        <v>5.733199999999999</v>
+        <v>5.897399999999999</v>
       </c>
       <c r="F48">
-        <v>7.553199999999999</v>
+        <v>7.7174</v>
       </c>
       <c r="G48">
         <v>0.127</v>
@@ -5211,37 +5211,37 @@
         <v>0.061</v>
       </c>
       <c r="M48">
-        <v>1.78104456</v>
+        <v>1.81976292</v>
       </c>
       <c r="N48">
-        <v>-1.72004456</v>
+        <v>-1.75876292</v>
       </c>
       <c r="O48">
-        <v>-0.2924075752</v>
+        <v>-0.2989896964000001</v>
       </c>
       <c r="P48">
-        <v>-1.4276369848</v>
+        <v>-1.4597732236</v>
       </c>
       <c r="Q48">
-        <v>-0.9716369847999999</v>
+        <v>-1.0037732236</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.337105799834877</v>
+        <v>0.3426021356808181</v>
       </c>
       <c r="T48">
-        <v>1.043259252051443</v>
+        <v>1.062943388882603</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.005822425913925478</v>
+        <v>0.005698544511501532</v>
       </c>
       <c r="W48">
-        <v>0.2344270719694964</v>
+        <v>0.234456283204188</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.0342495641995616</v>
+        <v>0.03352085006765604</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.291773585016802</v>
+        <v>0.293673585016802</v>
       </c>
       <c r="C49">
-        <v>3.742802169264479</v>
+        <v>3.491730935606634</v>
       </c>
       <c r="D49">
-        <v>11.33320216926448</v>
+        <v>11.24633093560663</v>
       </c>
       <c r="E49">
-        <v>5.897399999999999</v>
+        <v>6.061599999999999</v>
       </c>
       <c r="F49">
-        <v>7.7174</v>
+        <v>7.8816</v>
       </c>
       <c r="G49">
         <v>0.127</v>
@@ -5293,37 +5293,37 @@
         <v>0.061</v>
       </c>
       <c r="M49">
-        <v>1.81976292</v>
+        <v>1.85848128</v>
       </c>
       <c r="N49">
-        <v>-1.75876292</v>
+        <v>-1.79748128</v>
       </c>
       <c r="O49">
-        <v>-0.2989896964000001</v>
+        <v>-0.3055718176</v>
       </c>
       <c r="P49">
-        <v>-1.4597732236</v>
+        <v>-1.4919094624</v>
       </c>
       <c r="Q49">
-        <v>-1.0037732236</v>
+        <v>-1.0359094624</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3426021356808181</v>
+        <v>0.3483098690592954</v>
       </c>
       <c r="T49">
-        <v>1.062943388882603</v>
+        <v>1.083384607899576</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.005698544511501532</v>
+        <v>0.005579824834178584</v>
       </c>
       <c r="W49">
-        <v>0.234456283204188</v>
+        <v>0.2344842773041007</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.03352085006765604</v>
+        <v>0.0328224990245799</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.293673585016802</v>
+        <v>0.2955735850168019</v>
       </c>
       <c r="C50">
-        <v>3.491730935606634</v>
+        <v>3.241981341656523</v>
       </c>
       <c r="D50">
-        <v>11.24633093560663</v>
+        <v>11.16078134165652</v>
       </c>
       <c r="E50">
-        <v>6.061599999999999</v>
+        <v>6.225799999999998</v>
       </c>
       <c r="F50">
-        <v>7.881599999999999</v>
+        <v>8.045799999999998</v>
       </c>
       <c r="G50">
         <v>0.127</v>
@@ -5375,37 +5375,37 @@
         <v>0.061</v>
       </c>
       <c r="M50">
-        <v>1.85848128</v>
+        <v>1.89719964</v>
       </c>
       <c r="N50">
-        <v>-1.79748128</v>
+        <v>-1.83619964</v>
       </c>
       <c r="O50">
-        <v>-0.3055718176</v>
+        <v>-0.3121539388</v>
       </c>
       <c r="P50">
-        <v>-1.4919094624</v>
+        <v>-1.524045701199999</v>
       </c>
       <c r="Q50">
-        <v>-1.0359094624</v>
+        <v>-1.0680457012</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3483098690592954</v>
+        <v>0.3542414351192815</v>
       </c>
       <c r="T50">
-        <v>1.083384607899576</v>
+        <v>1.104627443348587</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.005579824834178584</v>
+        <v>0.005465950857970858</v>
       </c>
       <c r="W50">
-        <v>0.2344842773041007</v>
+        <v>0.2345111287876905</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.0328224990245799</v>
+        <v>0.03215265210571094</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2955735850168019</v>
+        <v>0.2974735850168019</v>
       </c>
       <c r="C51">
-        <v>3.241981341656523</v>
+        <v>2.993523454410498</v>
       </c>
       <c r="D51">
-        <v>11.16078134165652</v>
+        <v>11.0765234544105</v>
       </c>
       <c r="E51">
-        <v>6.225799999999998</v>
+        <v>6.389999999999999</v>
       </c>
       <c r="F51">
-        <v>8.045799999999998</v>
+        <v>8.209999999999999</v>
       </c>
       <c r="G51">
         <v>0.127</v>
@@ -5457,37 +5457,37 @@
         <v>0.061</v>
       </c>
       <c r="M51">
-        <v>1.89719964</v>
+        <v>1.935918</v>
       </c>
       <c r="N51">
-        <v>-1.83619964</v>
+        <v>-1.874918</v>
       </c>
       <c r="O51">
-        <v>-0.3121539388</v>
+        <v>-0.31873606</v>
       </c>
       <c r="P51">
-        <v>-1.524045701199999</v>
+        <v>-1.55618194</v>
       </c>
       <c r="Q51">
-        <v>-1.0680457012</v>
+        <v>-1.10018194</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3542414351192815</v>
+        <v>0.3604102638216671</v>
       </c>
       <c r="T51">
-        <v>1.104627443348587</v>
+        <v>1.126719992215559</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.005465950857970858</v>
+        <v>0.00535663184081144</v>
       </c>
       <c r="W51">
-        <v>0.2345111287876905</v>
+        <v>0.2345369062119367</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.03215265210571094</v>
+        <v>0.03150959906359663</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2974735850168019</v>
+        <v>0.2993735850168019</v>
       </c>
       <c r="C52">
-        <v>2.993523454410498</v>
+        <v>2.746328238004239</v>
       </c>
       <c r="D52">
-        <v>11.0765234544105</v>
+        <v>10.99352823800424</v>
       </c>
       <c r="E52">
-        <v>6.389999999999999</v>
+        <v>6.5542</v>
       </c>
       <c r="F52">
-        <v>8.209999999999999</v>
+        <v>8.3742</v>
       </c>
       <c r="G52">
         <v>0.127</v>
@@ -5539,37 +5539,37 @@
         <v>0.061</v>
       </c>
       <c r="M52">
-        <v>1.935918</v>
+        <v>1.97463636</v>
       </c>
       <c r="N52">
-        <v>-1.874918</v>
+        <v>-1.91363636</v>
       </c>
       <c r="O52">
-        <v>-0.31873606</v>
+        <v>-0.3253181812000001</v>
       </c>
       <c r="P52">
-        <v>-1.55618194</v>
+        <v>-1.5883181788</v>
       </c>
       <c r="Q52">
-        <v>-1.10018194</v>
+        <v>-1.1323181788</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3604102638216671</v>
+        <v>0.3668308814506808</v>
       </c>
       <c r="T52">
-        <v>1.126719992215559</v>
+        <v>1.149714277770978</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.00535663184081144</v>
+        <v>0.005251599843932783</v>
       </c>
       <c r="W52">
-        <v>0.2345369062119367</v>
+        <v>0.2345616727568007</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.03150959906359663</v>
+        <v>0.03089176378783987</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2993735850168019</v>
+        <v>0.301273585016802</v>
       </c>
       <c r="C53">
-        <v>2.746328238004239</v>
+        <v>2.500367520351828</v>
       </c>
       <c r="D53">
-        <v>10.99352823800424</v>
+        <v>10.91176752035183</v>
       </c>
       <c r="E53">
-        <v>6.5542</v>
+        <v>6.718399999999999</v>
       </c>
       <c r="F53">
-        <v>8.3742</v>
+        <v>8.538399999999999</v>
       </c>
       <c r="G53">
         <v>0.127</v>
@@ -5621,37 +5621,37 @@
         <v>0.061</v>
       </c>
       <c r="M53">
-        <v>1.97463636</v>
+        <v>2.01335472</v>
       </c>
       <c r="N53">
-        <v>-1.91363636</v>
+        <v>-1.95235472</v>
       </c>
       <c r="O53">
-        <v>-0.3253181812000001</v>
+        <v>-0.3319003024</v>
       </c>
       <c r="P53">
-        <v>-1.5883181788</v>
+        <v>-1.6204544176</v>
       </c>
       <c r="Q53">
-        <v>-1.1323181788</v>
+        <v>-1.1644544176</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3668308814506808</v>
+        <v>0.3735190248142367</v>
       </c>
       <c r="T53">
-        <v>1.149714277770978</v>
+        <v>1.173666658557874</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.005251599843932783</v>
+        <v>0.00515060753924177</v>
       </c>
       <c r="W53">
-        <v>0.2345616727568007</v>
+        <v>0.2345854867422468</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.03089176378783987</v>
+        <v>0.03029769140730454</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.301273585016802</v>
+        <v>0.3031735850168019</v>
       </c>
       <c r="C54">
-        <v>2.500367520351828</v>
+        <v>2.255613961262556</v>
       </c>
       <c r="D54">
-        <v>10.91176752035183</v>
+        <v>10.83121396126256</v>
       </c>
       <c r="E54">
-        <v>6.718399999999999</v>
+        <v>6.8826</v>
       </c>
       <c r="F54">
-        <v>8.538399999999999</v>
+        <v>8.7026</v>
       </c>
       <c r="G54">
         <v>0.127</v>
@@ -5703,37 +5703,37 @@
         <v>0.061</v>
       </c>
       <c r="M54">
-        <v>2.01335472</v>
+        <v>2.05207308</v>
       </c>
       <c r="N54">
-        <v>-1.95235472</v>
+        <v>-1.99107308</v>
       </c>
       <c r="O54">
-        <v>-0.3319003024</v>
+        <v>-0.3384824236</v>
       </c>
       <c r="P54">
-        <v>-1.6204544176</v>
+        <v>-1.6525906564</v>
       </c>
       <c r="Q54">
-        <v>-1.1644544176</v>
+        <v>-1.1965906564</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3735190248142367</v>
+        <v>0.3804917700230502</v>
       </c>
       <c r="T54">
-        <v>1.173666658557874</v>
+        <v>1.19863828959102</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.00515060753924177</v>
+        <v>0.005053426264916452</v>
       </c>
       <c r="W54">
-        <v>0.2345854867422468</v>
+        <v>0.2346084020867327</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.03029769140730454</v>
+        <v>0.02972603685244968</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3031735850168019</v>
+        <v>0.3050735850168019</v>
       </c>
       <c r="C55">
-        <v>2.255613961262556</v>
+        <v>2.012041021959599</v>
       </c>
       <c r="D55">
-        <v>10.83121396126256</v>
+        <v>10.7518410219596</v>
       </c>
       <c r="E55">
-        <v>6.8826</v>
+        <v>7.046799999999999</v>
       </c>
       <c r="F55">
-        <v>8.7026</v>
+        <v>8.8668</v>
       </c>
       <c r="G55">
         <v>0.127</v>
@@ -5785,37 +5785,37 @@
         <v>0.061</v>
       </c>
       <c r="M55">
-        <v>2.05207308</v>
+        <v>2.09079144</v>
       </c>
       <c r="N55">
-        <v>-1.99107308</v>
+        <v>-2.02979144</v>
       </c>
       <c r="O55">
-        <v>-0.3384824236</v>
+        <v>-0.3450645448</v>
       </c>
       <c r="P55">
-        <v>-1.6525906564</v>
+        <v>-1.6847268952</v>
       </c>
       <c r="Q55">
-        <v>-1.1965906564</v>
+        <v>-1.2287268952</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3804917700230502</v>
+        <v>0.3877676780670296</v>
       </c>
       <c r="T55">
-        <v>1.19863828959102</v>
+        <v>1.224695643712564</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.005053426264916452</v>
+        <v>0.004959844297047629</v>
       </c>
       <c r="W55">
-        <v>0.2346084020867327</v>
+        <v>0.2346304687147562</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.02972603685244968</v>
+        <v>0.0291755546885154</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3050735850168019</v>
+        <v>0.3069735850168019</v>
       </c>
       <c r="C56">
-        <v>2.012041021959599</v>
+        <v>1.769622935929156</v>
       </c>
       <c r="D56">
-        <v>10.7518410219596</v>
+        <v>10.67362293592916</v>
       </c>
       <c r="E56">
-        <v>7.046799999999999</v>
+        <v>7.211</v>
       </c>
       <c r="F56">
-        <v>8.8668</v>
+        <v>9.031000000000001</v>
       </c>
       <c r="G56">
         <v>0.127</v>
@@ -5867,37 +5867,37 @@
         <v>0.061</v>
       </c>
       <c r="M56">
-        <v>2.09079144</v>
+        <v>2.1295098</v>
       </c>
       <c r="N56">
-        <v>-2.02979144</v>
+        <v>-2.0685098</v>
       </c>
       <c r="O56">
-        <v>-0.3450645448</v>
+        <v>-0.3516466660000001</v>
       </c>
       <c r="P56">
-        <v>-1.6847268952</v>
+        <v>-1.716863134</v>
       </c>
       <c r="Q56">
-        <v>-1.2287268952</v>
+        <v>-1.260863134</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3877676780670296</v>
+        <v>0.3953669598018524</v>
       </c>
       <c r="T56">
-        <v>1.224695643712564</v>
+        <v>1.251911102461732</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.004959844297047629</v>
+        <v>0.004869665309828581</v>
       </c>
       <c r="W56">
-        <v>0.2346304687147562</v>
+        <v>0.2346517329199424</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.0291755546885154</v>
+        <v>0.02864509005781513</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3069735850168019</v>
+        <v>0.308873585016802</v>
       </c>
       <c r="C57">
-        <v>1.769622935929156</v>
+        <v>1.528334681032829</v>
       </c>
       <c r="D57">
-        <v>10.67362293592916</v>
+        <v>10.59653468103283</v>
       </c>
       <c r="E57">
-        <v>7.211</v>
+        <v>7.3752</v>
       </c>
       <c r="F57">
-        <v>9.031000000000001</v>
+        <v>9.1952</v>
       </c>
       <c r="G57">
         <v>0.127</v>
@@ -5949,37 +5949,37 @@
         <v>0.061</v>
       </c>
       <c r="M57">
-        <v>2.1295098</v>
+        <v>2.16822816</v>
       </c>
       <c r="N57">
-        <v>-2.0685098</v>
+        <v>-2.10722816</v>
       </c>
       <c r="O57">
-        <v>-0.3516466660000001</v>
+        <v>-0.3582287872</v>
       </c>
       <c r="P57">
-        <v>-1.716863134</v>
+        <v>-1.7489993728</v>
       </c>
       <c r="Q57">
-        <v>-1.260863134</v>
+        <v>-1.2929993728</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3953669598018524</v>
+        <v>0.4033116634337127</v>
       </c>
       <c r="T57">
-        <v>1.251911102461732</v>
+        <v>1.28036362751768</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.004869665309828581</v>
+        <v>0.0047827070007245</v>
       </c>
       <c r="W57">
-        <v>0.2346517329199424</v>
+        <v>0.2346722376892292</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.02864509005781513</v>
+        <v>0.02813357059249699</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.308873585016802</v>
+        <v>0.310773585016802</v>
       </c>
       <c r="C58">
-        <v>1.528334681032829</v>
+        <v>1.288151952819806</v>
       </c>
       <c r="D58">
-        <v>10.59653468103283</v>
+        <v>10.52055195281981</v>
       </c>
       <c r="E58">
-        <v>7.3752</v>
+        <v>7.539400000000001</v>
       </c>
       <c r="F58">
-        <v>9.1952</v>
+        <v>9.359400000000001</v>
       </c>
       <c r="G58">
         <v>0.127</v>
@@ -6031,37 +6031,37 @@
         <v>0.061</v>
       </c>
       <c r="M58">
-        <v>2.16822816</v>
+        <v>2.20694652</v>
       </c>
       <c r="N58">
-        <v>-2.10722816</v>
+        <v>-2.14594652</v>
       </c>
       <c r="O58">
-        <v>-0.3582287872</v>
+        <v>-0.3648109084000001</v>
       </c>
       <c r="P58">
-        <v>-1.7489993728</v>
+        <v>-1.7811356116</v>
       </c>
       <c r="Q58">
-        <v>-1.2929993728</v>
+        <v>-1.3251356116</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4033116634337127</v>
+        <v>0.4116258881647293</v>
       </c>
       <c r="T58">
-        <v>1.28036362751768</v>
+        <v>1.310139525832045</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0047827070007245</v>
+        <v>0.004698799860360911</v>
       </c>
       <c r="W58">
-        <v>0.2346722376892292</v>
+        <v>0.2346920229929269</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.02813357059249699</v>
+        <v>0.02763999917859361</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.310773585016802</v>
+        <v>0.312673585016802</v>
       </c>
       <c r="C59">
-        <v>1.288151952819806</v>
+        <v>1.049051138979051</v>
       </c>
       <c r="D59">
-        <v>10.52055195281981</v>
+        <v>10.44565113897905</v>
       </c>
       <c r="E59">
-        <v>7.539400000000001</v>
+        <v>7.7036</v>
       </c>
       <c r="F59">
-        <v>9.359400000000001</v>
+        <v>9.5236</v>
       </c>
       <c r="G59">
         <v>0.127</v>
@@ -6113,37 +6113,37 @@
         <v>0.061</v>
       </c>
       <c r="M59">
-        <v>2.20694652</v>
+        <v>2.24566488</v>
       </c>
       <c r="N59">
-        <v>-2.14594652</v>
+        <v>-2.18466488</v>
       </c>
       <c r="O59">
-        <v>-0.3648109084000001</v>
+        <v>-0.3713930296</v>
       </c>
       <c r="P59">
-        <v>-1.7811356116</v>
+        <v>-1.8132718504</v>
       </c>
       <c r="Q59">
-        <v>-1.3251356116</v>
+        <v>-1.3572718504</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4116258881647293</v>
+        <v>0.4203360283591276</v>
       </c>
       <c r="T59">
-        <v>1.310139525832045</v>
+        <v>1.341333324066142</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.004698799860360911</v>
+        <v>0.004617786069665035</v>
       </c>
       <c r="W59">
-        <v>0.2346920229929269</v>
+        <v>0.234711126044773</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.02763999917859361</v>
+        <v>0.02716344746861787</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3126735850168019</v>
+        <v>0.3145735850168019</v>
       </c>
       <c r="C60">
-        <v>1.049051138979056</v>
+        <v>0.8110092948751451</v>
       </c>
       <c r="D60">
-        <v>10.44565113897905</v>
+        <v>10.37180929487514</v>
       </c>
       <c r="E60">
-        <v>7.703599999999998</v>
+        <v>7.867799999999997</v>
       </c>
       <c r="F60">
-        <v>9.523599999999998</v>
+        <v>9.687799999999998</v>
       </c>
       <c r="G60">
         <v>0.127</v>
@@ -6195,37 +6195,37 @@
         <v>0.061</v>
       </c>
       <c r="M60">
-        <v>2.24566488</v>
+        <v>2.284383239999999</v>
       </c>
       <c r="N60">
-        <v>-2.18466488</v>
+        <v>-2.22338324</v>
       </c>
       <c r="O60">
-        <v>-0.3713930296</v>
+        <v>-0.3779751507999999</v>
       </c>
       <c r="P60">
-        <v>-1.8132718504</v>
+        <v>-1.8454080892</v>
       </c>
       <c r="Q60">
-        <v>-1.3572718504</v>
+        <v>-1.3894080892</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4203360283591275</v>
+        <v>0.4294710534410575</v>
       </c>
       <c r="T60">
-        <v>1.341333324066141</v>
+        <v>1.374048770994584</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.004617786069665035</v>
+        <v>0.004539518509162238</v>
       </c>
       <c r="W60">
-        <v>0.234711126044773</v>
+        <v>0.2347295815355395</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.02716344746861787</v>
+        <v>0.02670305005389551</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3145735850168019</v>
+        <v>0.3164735850168019</v>
       </c>
       <c r="C61">
-        <v>0.8110092948751451</v>
+        <v>0.5740041201144095</v>
       </c>
       <c r="D61">
-        <v>10.37180929487514</v>
+        <v>10.29900412011441</v>
       </c>
       <c r="E61">
-        <v>7.867799999999997</v>
+        <v>8.031999999999998</v>
       </c>
       <c r="F61">
-        <v>9.687799999999998</v>
+        <v>9.851999999999999</v>
       </c>
       <c r="G61">
         <v>0.127</v>
@@ -6277,37 +6277,37 @@
         <v>0.061</v>
       </c>
       <c r="M61">
-        <v>2.284383239999999</v>
+        <v>2.3231016</v>
       </c>
       <c r="N61">
-        <v>-2.22338324</v>
+        <v>-2.2621016</v>
       </c>
       <c r="O61">
-        <v>-0.3779751507999999</v>
+        <v>-0.384557272</v>
       </c>
       <c r="P61">
-        <v>-1.8454080892</v>
+        <v>-1.877544328</v>
       </c>
       <c r="Q61">
-        <v>-1.3894080892</v>
+        <v>-1.421544328</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4294710534410575</v>
+        <v>0.4390628297770839</v>
       </c>
       <c r="T61">
-        <v>1.374048770994584</v>
+        <v>1.408399990269448</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.004539518509162238</v>
+        <v>0.004463859867342867</v>
       </c>
       <c r="W61">
-        <v>0.2347295815355395</v>
+        <v>0.2347474218432806</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.02670305005389551</v>
+        <v>0.02625799921966387</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3164735850168019</v>
+        <v>0.3183735850168019</v>
       </c>
       <c r="C62">
-        <v>0.5740041201144095</v>
+        <v>0.3380139360912207</v>
       </c>
       <c r="D62">
-        <v>10.29900412011441</v>
+        <v>10.22721393609122</v>
       </c>
       <c r="E62">
-        <v>8.031999999999998</v>
+        <v>8.196199999999997</v>
       </c>
       <c r="F62">
-        <v>9.851999999999999</v>
+        <v>10.0162</v>
       </c>
       <c r="G62">
         <v>0.127</v>
@@ -6359,37 +6359,37 @@
         <v>0.061</v>
       </c>
       <c r="M62">
-        <v>2.3231016</v>
+        <v>2.36181996</v>
       </c>
       <c r="N62">
-        <v>-2.2621016</v>
+        <v>-2.30081996</v>
       </c>
       <c r="O62">
-        <v>-0.384557272</v>
+        <v>-0.3911393932</v>
       </c>
       <c r="P62">
-        <v>-1.877544328</v>
+        <v>-1.9096805668</v>
       </c>
       <c r="Q62">
-        <v>-1.421544328</v>
+        <v>-1.4536805668</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4390628297770839</v>
+        <v>0.4491464920790605</v>
       </c>
       <c r="T62">
-        <v>1.408399990269448</v>
+        <v>1.444512810532768</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.004463859867342867</v>
+        <v>0.00439068183673069</v>
       </c>
       <c r="W62">
-        <v>0.2347474218432806</v>
+        <v>0.2347646772228989</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.02625799921966387</v>
+        <v>0.02582754021606282</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3183735850168019</v>
+        <v>0.3202735850168019</v>
       </c>
       <c r="C63">
-        <v>0.3380139360912207</v>
+        <v>0.1030176644668153</v>
       </c>
       <c r="D63">
-        <v>10.22721393609122</v>
+        <v>10.15641766446681</v>
       </c>
       <c r="E63">
-        <v>8.196199999999997</v>
+        <v>8.360399999999998</v>
       </c>
       <c r="F63">
-        <v>10.0162</v>
+        <v>10.1804</v>
       </c>
       <c r="G63">
         <v>0.127</v>
@@ -6441,37 +6441,37 @@
         <v>0.061</v>
       </c>
       <c r="M63">
-        <v>2.36181996</v>
+        <v>2.40053832</v>
       </c>
       <c r="N63">
-        <v>-2.30081996</v>
+        <v>-2.33953832</v>
       </c>
       <c r="O63">
-        <v>-0.3911393932</v>
+        <v>-0.3977215144</v>
       </c>
       <c r="P63">
-        <v>-1.9096805668</v>
+        <v>-1.9418168056</v>
       </c>
       <c r="Q63">
-        <v>-1.4536805668</v>
+        <v>-1.4858168056</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4491464920790605</v>
+        <v>0.4597608734495621</v>
       </c>
       <c r="T63">
-        <v>1.444512810532768</v>
+        <v>1.482526305546788</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.00439068183673069</v>
+        <v>0.004319864387751162</v>
       </c>
       <c r="W63">
-        <v>0.2347646772228989</v>
+        <v>0.2347813759773683</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.02582754021606282</v>
+        <v>0.02541096698677148</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3202735850168019</v>
+        <v>0.3221735850168019</v>
       </c>
       <c r="C64">
-        <v>0.1030176644668153</v>
+        <v>-0.1310051934641052</v>
       </c>
       <c r="D64">
-        <v>10.15641766446681</v>
+        <v>10.08659480653589</v>
       </c>
       <c r="E64">
-        <v>8.360399999999998</v>
+        <v>8.5246</v>
       </c>
       <c r="F64">
-        <v>10.1804</v>
+        <v>10.3446</v>
       </c>
       <c r="G64">
         <v>0.127</v>
@@ -6523,37 +6523,37 @@
         <v>0.061</v>
       </c>
       <c r="M64">
-        <v>2.40053832</v>
+        <v>2.43925668</v>
       </c>
       <c r="N64">
-        <v>-2.33953832</v>
+        <v>-2.37825668</v>
       </c>
       <c r="O64">
-        <v>-0.3977215144</v>
+        <v>-0.4043036356</v>
       </c>
       <c r="P64">
-        <v>-1.9418168056</v>
+        <v>-1.9739530444</v>
       </c>
       <c r="Q64">
-        <v>-1.4858168056</v>
+        <v>-1.5179530444</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4597608734495621</v>
+        <v>0.4709490051644151</v>
       </c>
       <c r="T64">
-        <v>1.482526305546788</v>
+        <v>1.522594584075079</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.004319864387751162</v>
+        <v>0.004251295111755111</v>
       </c>
       <c r="W64">
-        <v>0.2347813759773683</v>
+        <v>0.2347975446126482</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.02541096698677148</v>
+        <v>0.02500761830444176</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3221735850168019</v>
+        <v>0.3240735850168019</v>
       </c>
       <c r="C65">
-        <v>-0.1310051934641052</v>
+        <v>-0.3640745765615403</v>
       </c>
       <c r="D65">
-        <v>10.08659480653589</v>
+        <v>10.01772542343846</v>
       </c>
       <c r="E65">
-        <v>8.5246</v>
+        <v>8.688799999999999</v>
       </c>
       <c r="F65">
-        <v>10.3446</v>
+        <v>10.5088</v>
       </c>
       <c r="G65">
         <v>0.127</v>
@@ -6605,37 +6605,37 @@
         <v>0.061</v>
       </c>
       <c r="M65">
-        <v>2.43925668</v>
+        <v>2.47797504</v>
       </c>
       <c r="N65">
-        <v>-2.37825668</v>
+        <v>-2.41697504</v>
       </c>
       <c r="O65">
-        <v>-0.4043036356</v>
+        <v>-0.4108857568000001</v>
       </c>
       <c r="P65">
-        <v>-1.9739530444</v>
+        <v>-2.0060892832</v>
       </c>
       <c r="Q65">
-        <v>-1.5179530444</v>
+        <v>-1.5500892832</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4709490051644151</v>
+        <v>0.4827586997523155</v>
       </c>
       <c r="T65">
-        <v>1.522594584075079</v>
+        <v>1.564888878077165</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.004251295111755111</v>
+        <v>0.004184868625633937</v>
       </c>
       <c r="W65">
-        <v>0.2347975446126482</v>
+        <v>0.2348132079780755</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.02500761830444176</v>
+        <v>0.02461687426843495</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3240735850168019</v>
+        <v>0.325973585016802</v>
       </c>
       <c r="C66">
-        <v>-0.3640745765615403</v>
+        <v>-0.5962098828231621</v>
       </c>
       <c r="D66">
-        <v>10.01772542343846</v>
+        <v>9.949790117176837</v>
       </c>
       <c r="E66">
-        <v>8.688799999999999</v>
+        <v>8.853</v>
       </c>
       <c r="F66">
-        <v>10.5088</v>
+        <v>10.673</v>
       </c>
       <c r="G66">
         <v>0.127</v>
@@ -6687,37 +6687,37 @@
         <v>0.061</v>
       </c>
       <c r="M66">
-        <v>2.47797504</v>
+        <v>2.5166934</v>
       </c>
       <c r="N66">
-        <v>-2.41697504</v>
+        <v>-2.4556934</v>
       </c>
       <c r="O66">
-        <v>-0.4108857568000001</v>
+        <v>-0.4174678780000001</v>
       </c>
       <c r="P66">
-        <v>-2.0060892832</v>
+        <v>-2.038225522</v>
       </c>
       <c r="Q66">
-        <v>-1.5500892832</v>
+        <v>-1.582225522</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4827586997523155</v>
+        <v>0.4952432340309532</v>
       </c>
       <c r="T66">
-        <v>1.564888878077165</v>
+        <v>1.60959998887937</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.004184868625633937</v>
+        <v>0.004120486031393414</v>
       </c>
       <c r="W66">
-        <v>0.2348132079780755</v>
+        <v>0.2348283893937975</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.02461687426843495</v>
+        <v>0.02423815312584354</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.325973585016802</v>
+        <v>0.3278735850168019</v>
       </c>
       <c r="C67">
-        <v>-0.5962098828231621</v>
+        <v>-0.8274299876001088</v>
       </c>
       <c r="D67">
-        <v>9.949790117176837</v>
+        <v>9.88277001239989</v>
       </c>
       <c r="E67">
-        <v>8.853</v>
+        <v>9.017199999999999</v>
       </c>
       <c r="F67">
-        <v>10.673</v>
+        <v>10.8372</v>
       </c>
       <c r="G67">
         <v>0.127</v>
@@ -6769,37 +6769,37 @@
         <v>0.061</v>
       </c>
       <c r="M67">
-        <v>2.5166934</v>
+        <v>2.55541176</v>
       </c>
       <c r="N67">
-        <v>-2.4556934</v>
+        <v>-2.49441176</v>
       </c>
       <c r="O67">
-        <v>-0.4174678780000001</v>
+        <v>-0.4240499992000001</v>
       </c>
       <c r="P67">
-        <v>-2.038225522</v>
+        <v>-2.0703617608</v>
       </c>
       <c r="Q67">
-        <v>-1.582225522</v>
+        <v>-1.6143617608</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4952432340309532</v>
+        <v>0.5084621526789223</v>
       </c>
       <c r="T67">
-        <v>1.60959998887937</v>
+        <v>1.65694116502288</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.004120486031393414</v>
+        <v>0.004058054424857151</v>
       </c>
       <c r="W67">
-        <v>0.2348283893937975</v>
+        <v>0.2348431107666187</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.02423815312584354</v>
+        <v>0.02387090838151262</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3278735850168019</v>
+        <v>0.3297735850168019</v>
       </c>
       <c r="C68">
-        <v>-0.8274299876001088</v>
+        <v>-1.05775326108151</v>
       </c>
       <c r="D68">
-        <v>9.88277001239989</v>
+        <v>9.816646738918489</v>
       </c>
       <c r="E68">
-        <v>9.017199999999999</v>
+        <v>9.1814</v>
       </c>
       <c r="F68">
-        <v>10.8372</v>
+        <v>11.0014</v>
       </c>
       <c r="G68">
         <v>0.127</v>
@@ -6851,37 +6851,37 @@
         <v>0.061</v>
       </c>
       <c r="M68">
-        <v>2.55541176</v>
+        <v>2.59413012</v>
       </c>
       <c r="N68">
-        <v>-2.49441176</v>
+        <v>-2.53313012</v>
       </c>
       <c r="O68">
-        <v>-0.4240499992000001</v>
+        <v>-0.4306321204</v>
       </c>
       <c r="P68">
-        <v>-2.0703617608</v>
+        <v>-2.1024979996</v>
       </c>
       <c r="Q68">
-        <v>-1.6143617608</v>
+        <v>-1.6464979996</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5084621526789223</v>
+        <v>0.5224822179116169</v>
       </c>
       <c r="T68">
-        <v>1.65694116502288</v>
+        <v>1.707151503356907</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.004058054424857151</v>
+        <v>0.003997486448366746</v>
       </c>
       <c r="W68">
-        <v>0.2348431107666187</v>
+        <v>0.2348573926954751</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.02387090838151262</v>
+        <v>0.02351462616686317</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3297735850168019</v>
+        <v>0.3316735850168019</v>
       </c>
       <c r="C69">
-        <v>-1.05775326108151</v>
+        <v>-1.287197585081746</v>
       </c>
       <c r="D69">
-        <v>9.816646738918489</v>
+        <v>9.751402414918253</v>
       </c>
       <c r="E69">
-        <v>9.1814</v>
+        <v>9.345599999999999</v>
       </c>
       <c r="F69">
-        <v>11.0014</v>
+        <v>11.1656</v>
       </c>
       <c r="G69">
         <v>0.127</v>
@@ -6933,37 +6933,37 @@
         <v>0.061</v>
       </c>
       <c r="M69">
-        <v>2.59413012</v>
+        <v>2.63284848</v>
       </c>
       <c r="N69">
-        <v>-2.53313012</v>
+        <v>-2.57184848</v>
       </c>
       <c r="O69">
-        <v>-0.4306321204</v>
+        <v>-0.4372142416</v>
       </c>
       <c r="P69">
-        <v>-2.1024979996</v>
+        <v>-2.1346342384</v>
       </c>
       <c r="Q69">
-        <v>-1.6464979996</v>
+        <v>-1.6786342384</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5224822179116169</v>
+        <v>0.537378537221355</v>
       </c>
       <c r="T69">
-        <v>1.707151503356907</v>
+        <v>1.760499987836811</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.003997486448366746</v>
+        <v>0.003938699882949589</v>
       </c>
       <c r="W69">
-        <v>0.2348573926954751</v>
+        <v>0.2348712545676005</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.02351462616686317</v>
+        <v>0.02316882284087995</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3316735850168019</v>
+        <v>0.3335735850168019</v>
       </c>
       <c r="C70">
-        <v>-1.287197585081746</v>
+        <v>-1.515780369162721</v>
       </c>
       <c r="D70">
-        <v>9.751402414918253</v>
+        <v>9.687019630837279</v>
       </c>
       <c r="E70">
-        <v>9.345599999999999</v>
+        <v>9.5098</v>
       </c>
       <c r="F70">
-        <v>11.1656</v>
+        <v>11.3298</v>
       </c>
       <c r="G70">
         <v>0.127</v>
@@ -7015,37 +7015,37 @@
         <v>0.061</v>
       </c>
       <c r="M70">
-        <v>2.63284848</v>
+        <v>2.67156684</v>
       </c>
       <c r="N70">
-        <v>-2.57184848</v>
+        <v>-2.61056684</v>
       </c>
       <c r="O70">
-        <v>-0.4372142416</v>
+        <v>-0.4437963628000001</v>
       </c>
       <c r="P70">
-        <v>-2.1346342384</v>
+        <v>-2.1667704772</v>
       </c>
       <c r="Q70">
-        <v>-1.6786342384</v>
+        <v>-1.7107704772</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.537378537221355</v>
+        <v>0.5532359093897858</v>
       </c>
       <c r="T70">
-        <v>1.760499987836811</v>
+        <v>1.817290310025095</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.003938699882949589</v>
+        <v>0.003881617275950318</v>
       </c>
       <c r="W70">
-        <v>0.2348712545676005</v>
+        <v>0.2348847146463309</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.02316882284087995</v>
+        <v>0.02283304279970777</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3335735850168019</v>
+        <v>0.3354735850168019</v>
       </c>
       <c r="C71">
-        <v>-1.515780369162721</v>
+        <v>-1.743518566121629</v>
       </c>
       <c r="D71">
-        <v>9.687019630837279</v>
+        <v>9.62348143387837</v>
       </c>
       <c r="E71">
-        <v>9.5098</v>
+        <v>9.673999999999999</v>
       </c>
       <c r="F71">
-        <v>11.3298</v>
+        <v>11.494</v>
       </c>
       <c r="G71">
         <v>0.127</v>
@@ -7097,37 +7097,37 @@
         <v>0.061</v>
       </c>
       <c r="M71">
-        <v>2.67156684</v>
+        <v>2.7102852</v>
       </c>
       <c r="N71">
-        <v>-2.61056684</v>
+        <v>-2.6492852</v>
       </c>
       <c r="O71">
-        <v>-0.4437963628000001</v>
+        <v>-0.450378484</v>
       </c>
       <c r="P71">
-        <v>-2.1667704772</v>
+        <v>-2.198906716</v>
       </c>
       <c r="Q71">
-        <v>-1.7107704772</v>
+        <v>-1.742906716</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5532359093897858</v>
+        <v>0.5701504397027787</v>
       </c>
       <c r="T71">
-        <v>1.817290310025095</v>
+        <v>1.877866653692598</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.003881617275950318</v>
+        <v>0.0038261656005796</v>
       </c>
       <c r="W71">
-        <v>0.2348847146463309</v>
+        <v>0.2348977901513833</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.02283304279970777</v>
+        <v>0.02250685647399764</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3354735850168019</v>
+        <v>0.3373735850168019</v>
       </c>
       <c r="C72">
-        <v>-1.743518566121629</v>
+        <v>-1.970428686873193</v>
       </c>
       <c r="D72">
-        <v>9.62348143387837</v>
+        <v>9.560771313126807</v>
       </c>
       <c r="E72">
-        <v>9.673999999999999</v>
+        <v>9.838200000000001</v>
       </c>
       <c r="F72">
-        <v>11.494</v>
+        <v>11.6582</v>
       </c>
       <c r="G72">
         <v>0.127</v>
@@ -7179,37 +7179,37 @@
         <v>0.061</v>
       </c>
       <c r="M72">
-        <v>2.7102852</v>
+        <v>2.74900356</v>
       </c>
       <c r="N72">
-        <v>-2.6492852</v>
+        <v>-2.68800356</v>
       </c>
       <c r="O72">
-        <v>-0.450378484</v>
+        <v>-0.4569606052000001</v>
       </c>
       <c r="P72">
-        <v>-2.198906716</v>
+        <v>-2.2310429548</v>
       </c>
       <c r="Q72">
-        <v>-1.742906716</v>
+        <v>-1.7750429548</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5701504397027787</v>
+        <v>0.5882314893477021</v>
       </c>
       <c r="T72">
-        <v>1.877866653692598</v>
+        <v>1.942620676233722</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0038261656005796</v>
+        <v>0.003772275944233408</v>
       </c>
       <c r="W72">
-        <v>0.2348977901513833</v>
+        <v>0.2349104973323498</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.02250685647399764</v>
+        <v>0.0221898584954906</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3373735850168019</v>
+        <v>0.3392735850168019</v>
       </c>
       <c r="C73">
-        <v>-1.970428686873186</v>
+        <v>-2.196526814753765</v>
       </c>
       <c r="D73">
-        <v>9.560771313126811</v>
+        <v>9.498873185246232</v>
       </c>
       <c r="E73">
-        <v>9.838199999999997</v>
+        <v>10.0024</v>
       </c>
       <c r="F73">
-        <v>11.6582</v>
+        <v>11.8224</v>
       </c>
       <c r="G73">
         <v>0.127</v>
@@ -7261,37 +7261,37 @@
         <v>0.061</v>
       </c>
       <c r="M73">
-        <v>2.749003559999999</v>
+        <v>2.78772192</v>
       </c>
       <c r="N73">
-        <v>-2.688003559999999</v>
+        <v>-2.72672192</v>
       </c>
       <c r="O73">
-        <v>-0.4569606051999999</v>
+        <v>-0.4635427264</v>
       </c>
       <c r="P73">
-        <v>-2.231042954799999</v>
+        <v>-2.2631791936</v>
       </c>
       <c r="Q73">
-        <v>-1.7750429548</v>
+        <v>-1.8071791936</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5882314893477019</v>
+        <v>0.6076040425386913</v>
       </c>
       <c r="T73">
-        <v>1.942620676233722</v>
+        <v>2.011999986099212</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.003772275944233409</v>
+        <v>0.003719883222785722</v>
       </c>
       <c r="W73">
-        <v>0.2349104973323498</v>
+        <v>0.2349228515360672</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0221898584954906</v>
+        <v>0.02188166601638664</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3392735850168019</v>
+        <v>0.341173585016802</v>
       </c>
       <c r="C74">
-        <v>-2.196526814753765</v>
+        <v>-2.421828619273425</v>
       </c>
       <c r="D74">
-        <v>9.498873185246232</v>
+        <v>9.437771380726572</v>
       </c>
       <c r="E74">
-        <v>10.0024</v>
+        <v>10.1666</v>
       </c>
       <c r="F74">
-        <v>11.8224</v>
+        <v>11.9866</v>
       </c>
       <c r="G74">
         <v>0.127</v>
@@ -7343,37 +7343,37 @@
         <v>0.061</v>
       </c>
       <c r="M74">
-        <v>2.78772192</v>
+        <v>2.826440279999999</v>
       </c>
       <c r="N74">
-        <v>-2.72672192</v>
+        <v>-2.76544028</v>
       </c>
       <c r="O74">
-        <v>-0.4635427264</v>
+        <v>-0.4701248476</v>
       </c>
       <c r="P74">
-        <v>-2.2631791936</v>
+        <v>-2.2953154324</v>
       </c>
       <c r="Q74">
-        <v>-1.8071791936</v>
+        <v>-1.8393154324</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6076040425386913</v>
+        <v>0.6284115996697539</v>
       </c>
       <c r="T74">
-        <v>2.011999986099212</v>
+        <v>2.086518504102886</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.003719883222785722</v>
+        <v>0.003668925918364</v>
       </c>
       <c r="W74">
-        <v>0.2349228515360672</v>
+        <v>0.2349348672684498</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.02188166601638664</v>
+        <v>0.02158191716684699</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.341173585016802</v>
+        <v>0.3430735850168019</v>
       </c>
       <c r="C75">
-        <v>-2.421828619273425</v>
+        <v>-2.646349369340626</v>
       </c>
       <c r="D75">
-        <v>9.437771380726572</v>
+        <v>9.377450630659371</v>
       </c>
       <c r="E75">
-        <v>10.1666</v>
+        <v>10.3308</v>
       </c>
       <c r="F75">
-        <v>11.9866</v>
+        <v>12.1508</v>
       </c>
       <c r="G75">
         <v>0.127</v>
@@ -7425,37 +7425,37 @@
         <v>0.061</v>
       </c>
       <c r="M75">
-        <v>2.826440279999999</v>
+        <v>2.86515864</v>
       </c>
       <c r="N75">
-        <v>-2.76544028</v>
+        <v>-2.80415864</v>
       </c>
       <c r="O75">
-        <v>-0.4701248476</v>
+        <v>-0.4767069688</v>
       </c>
       <c r="P75">
-        <v>-2.2953154324</v>
+        <v>-2.3274516712</v>
       </c>
       <c r="Q75">
-        <v>-1.8393154324</v>
+        <v>-1.8714516712</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6284115996697539</v>
+        <v>0.6508197381185905</v>
       </c>
       <c r="T75">
-        <v>2.086518504102886</v>
+        <v>2.166769215799151</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.003668925918364</v>
+        <v>0.003619345838386108</v>
       </c>
       <c r="W75">
-        <v>0.2349348672684498</v>
+        <v>0.2349465582513086</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.02158191716684699</v>
+        <v>0.02129026963756531</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3430735850168019</v>
+        <v>0.3449735850168019</v>
       </c>
       <c r="C76">
-        <v>-2.646349369340626</v>
+        <v>-2.870103945982988</v>
       </c>
       <c r="D76">
-        <v>9.377450630659371</v>
+        <v>9.317896054017009</v>
       </c>
       <c r="E76">
-        <v>10.3308</v>
+        <v>10.495</v>
       </c>
       <c r="F76">
-        <v>12.1508</v>
+        <v>12.315</v>
       </c>
       <c r="G76">
         <v>0.127</v>
@@ -7507,37 +7507,37 @@
         <v>0.061</v>
       </c>
       <c r="M76">
-        <v>2.86515864</v>
+        <v>2.903877</v>
       </c>
       <c r="N76">
-        <v>-2.80415864</v>
+        <v>-2.842877</v>
       </c>
       <c r="O76">
-        <v>-0.4767069688</v>
+        <v>-0.48328909</v>
       </c>
       <c r="P76">
-        <v>-2.3274516712</v>
+        <v>-2.35958791</v>
       </c>
       <c r="Q76">
-        <v>-1.8714516712</v>
+        <v>-1.90358791</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6508197381185905</v>
+        <v>0.6750205276433342</v>
       </c>
       <c r="T76">
-        <v>2.166769215799151</v>
+        <v>2.253439984431117</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.003619345838386108</v>
+        <v>0.003571087893874293</v>
       </c>
       <c r="W76">
-        <v>0.2349465582513086</v>
+        <v>0.2349579374746245</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.02129026963756531</v>
+        <v>0.02100639937573112</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3449735850168019</v>
+        <v>0.3468735850168019</v>
       </c>
       <c r="C77">
-        <v>-2.870103945982988</v>
+        <v>-3.093106854586361</v>
       </c>
       <c r="D77">
-        <v>9.317896054017009</v>
+        <v>9.259093145413637</v>
       </c>
       <c r="E77">
-        <v>10.495</v>
+        <v>10.6592</v>
       </c>
       <c r="F77">
-        <v>12.315</v>
+        <v>12.4792</v>
       </c>
       <c r="G77">
         <v>0.127</v>
@@ -7589,37 +7589,37 @@
         <v>0.061</v>
       </c>
       <c r="M77">
-        <v>2.903877</v>
+        <v>2.94259536</v>
       </c>
       <c r="N77">
-        <v>-2.842877</v>
+        <v>-2.88159536</v>
       </c>
       <c r="O77">
-        <v>-0.48328909</v>
+        <v>-0.4898712112</v>
       </c>
       <c r="P77">
-        <v>-2.35958791</v>
+        <v>-2.3917241488</v>
       </c>
       <c r="Q77">
-        <v>-1.90358791</v>
+        <v>-1.9357241488</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6750205276433342</v>
+        <v>0.7012380496284734</v>
       </c>
       <c r="T77">
-        <v>2.253439984431117</v>
+        <v>2.347333317115748</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.003571087893874293</v>
+        <v>0.003524099895270684</v>
       </c>
       <c r="W77">
-        <v>0.2349579374746245</v>
+        <v>0.2349690172446952</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.02100639937573112</v>
+        <v>0.02072999938394515</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3468735850168019</v>
+        <v>0.3487735850168019</v>
       </c>
       <c r="C78">
-        <v>-3.093106854586361</v>
+        <v>-3.315372236673419</v>
       </c>
       <c r="D78">
-        <v>9.259093145413637</v>
+        <v>9.20102776332658</v>
       </c>
       <c r="E78">
-        <v>10.6592</v>
+        <v>10.8234</v>
       </c>
       <c r="F78">
-        <v>12.4792</v>
+        <v>12.6434</v>
       </c>
       <c r="G78">
         <v>0.127</v>
@@ -7671,37 +7671,37 @@
         <v>0.061</v>
       </c>
       <c r="M78">
-        <v>2.94259536</v>
+        <v>2.98131372</v>
       </c>
       <c r="N78">
-        <v>-2.88159536</v>
+        <v>-2.92031372</v>
       </c>
       <c r="O78">
-        <v>-0.4898712112</v>
+        <v>-0.4964533324000001</v>
       </c>
       <c r="P78">
-        <v>-2.3917241488</v>
+        <v>-2.4238603876</v>
       </c>
       <c r="Q78">
-        <v>-1.9357241488</v>
+        <v>-1.9678603876</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7012380496284734</v>
+        <v>0.729735356134059</v>
       </c>
       <c r="T78">
-        <v>2.347333317115748</v>
+        <v>2.449391287425128</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.003524099895270684</v>
+        <v>0.003478332364163272</v>
       </c>
       <c r="W78">
-        <v>0.2349690172446952</v>
+        <v>0.2349798092285303</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.02072999938394515</v>
+        <v>0.02046077861272511</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3487735850168019</v>
+        <v>0.3506735850168019</v>
       </c>
       <c r="C79">
-        <v>-3.315372236673419</v>
+        <v>-3.536913881241796</v>
       </c>
       <c r="D79">
-        <v>9.20102776332658</v>
+        <v>9.143686118758202</v>
       </c>
       <c r="E79">
-        <v>10.8234</v>
+        <v>10.9876</v>
       </c>
       <c r="F79">
-        <v>12.6434</v>
+        <v>12.8076</v>
       </c>
       <c r="G79">
         <v>0.127</v>
@@ -7753,37 +7753,37 @@
         <v>0.061</v>
       </c>
       <c r="M79">
-        <v>2.98131372</v>
+        <v>3.02003208</v>
       </c>
       <c r="N79">
-        <v>-2.92031372</v>
+        <v>-2.95903208</v>
       </c>
       <c r="O79">
-        <v>-0.4964533324000001</v>
+        <v>-0.5030354536</v>
       </c>
       <c r="P79">
-        <v>-2.4238603876</v>
+        <v>-2.4559966264</v>
       </c>
       <c r="Q79">
-        <v>-1.9678603876</v>
+        <v>-1.9999966264</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.729735356134059</v>
+        <v>0.7608233268674254</v>
       </c>
       <c r="T79">
-        <v>2.449391287425128</v>
+        <v>2.560727255035361</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.003478332364163272</v>
+        <v>0.003433738359494513</v>
       </c>
       <c r="W79">
-        <v>0.2349798092285303</v>
+        <v>0.2349903244948312</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.02046077861272511</v>
+        <v>0.02019846093820299</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3506735850168019</v>
+        <v>0.3525735850168019</v>
       </c>
       <c r="C80">
-        <v>-3.536913881241796</v>
+        <v>-3.757745235680899</v>
       </c>
       <c r="D80">
-        <v>9.143686118758202</v>
+        <v>9.087054764319101</v>
       </c>
       <c r="E80">
-        <v>10.9876</v>
+        <v>11.1518</v>
       </c>
       <c r="F80">
-        <v>12.8076</v>
+        <v>12.9718</v>
       </c>
       <c r="G80">
         <v>0.127</v>
@@ -7835,37 +7835,37 @@
         <v>0.061</v>
       </c>
       <c r="M80">
-        <v>3.02003208</v>
+        <v>3.05875044</v>
       </c>
       <c r="N80">
-        <v>-2.95903208</v>
+        <v>-2.99775044</v>
       </c>
       <c r="O80">
-        <v>-0.5030354536</v>
+        <v>-0.5096175748000001</v>
       </c>
       <c r="P80">
-        <v>-2.4559966264</v>
+        <v>-2.4881328652</v>
       </c>
       <c r="Q80">
-        <v>-1.9999966264</v>
+        <v>-2.0321328652</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7608233268674254</v>
+        <v>0.7948720567182551</v>
       </c>
       <c r="T80">
-        <v>2.560727255035361</v>
+        <v>2.682666648132283</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.003433738359494513</v>
+        <v>0.003390273316969265</v>
       </c>
       <c r="W80">
-        <v>0.2349903244948312</v>
+        <v>0.2350005735518587</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.02019846093820299</v>
+        <v>0.0199427842174662</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3525735850168019</v>
+        <v>0.3544735850168019</v>
       </c>
       <c r="C81">
-        <v>-3.757745235680899</v>
+        <v>-3.977879416285523</v>
       </c>
       <c r="D81">
-        <v>9.087054764319101</v>
+        <v>9.031120583714475</v>
       </c>
       <c r="E81">
-        <v>11.1518</v>
+        <v>11.316</v>
       </c>
       <c r="F81">
-        <v>12.9718</v>
+        <v>13.136</v>
       </c>
       <c r="G81">
         <v>0.127</v>
@@ -7917,37 +7917,37 @@
         <v>0.061</v>
       </c>
       <c r="M81">
-        <v>3.05875044</v>
+        <v>3.0974688</v>
       </c>
       <c r="N81">
-        <v>-2.99775044</v>
+        <v>-3.0364688</v>
       </c>
       <c r="O81">
-        <v>-0.5096175748000001</v>
+        <v>-0.516199696</v>
       </c>
       <c r="P81">
-        <v>-2.4881328652</v>
+        <v>-2.520269104</v>
       </c>
       <c r="Q81">
-        <v>-2.0321328652</v>
+        <v>-2.064269104</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7948720567182551</v>
+        <v>0.832325659554168</v>
       </c>
       <c r="T81">
-        <v>2.682666648132283</v>
+        <v>2.816799980538897</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.003390273316969265</v>
+        <v>0.003347894900507149</v>
       </c>
       <c r="W81">
-        <v>0.2350005735518587</v>
+        <v>0.2350105663824604</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.0199427842174662</v>
+        <v>0.01969349941474796</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3544735850168019</v>
+        <v>0.3563735850168019</v>
       </c>
       <c r="C82">
-        <v>-3.977879416285523</v>
+        <v>-4.197329218383564</v>
       </c>
       <c r="D82">
-        <v>9.031120583714475</v>
+        <v>8.975870781616436</v>
       </c>
       <c r="E82">
-        <v>11.316</v>
+        <v>11.4802</v>
       </c>
       <c r="F82">
-        <v>13.136</v>
+        <v>13.3002</v>
       </c>
       <c r="G82">
         <v>0.127</v>
@@ -7999,37 +7999,37 @@
         <v>0.061</v>
       </c>
       <c r="M82">
-        <v>3.0974688</v>
+        <v>3.13618716</v>
       </c>
       <c r="N82">
-        <v>-3.0364688</v>
+        <v>-3.07518716</v>
       </c>
       <c r="O82">
-        <v>-0.516199696</v>
+        <v>-0.5227818172000001</v>
       </c>
       <c r="P82">
-        <v>-2.520269104</v>
+        <v>-2.5524053428</v>
       </c>
       <c r="Q82">
-        <v>-2.064269104</v>
+        <v>-2.0964053428</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.832325659554168</v>
+        <v>0.8737217468991242</v>
       </c>
       <c r="T82">
-        <v>2.816799980538897</v>
+        <v>2.965052611093576</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.003347894900507149</v>
+        <v>0.00330656286469842</v>
       </c>
       <c r="W82">
-        <v>0.2350105663824604</v>
+        <v>0.2350203124765041</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.01969349941474796</v>
+        <v>0.0194503697923436</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3563735850168019</v>
+        <v>0.358273585016802</v>
       </c>
       <c r="C83">
-        <v>-4.197329218383564</v>
+        <v>-4.416107126094241</v>
       </c>
       <c r="D83">
-        <v>8.975870781616436</v>
+        <v>8.921292873905758</v>
       </c>
       <c r="E83">
-        <v>11.4802</v>
+        <v>11.6444</v>
       </c>
       <c r="F83">
-        <v>13.3002</v>
+        <v>13.4644</v>
       </c>
       <c r="G83">
         <v>0.127</v>
@@ -8081,37 +8081,37 @@
         <v>0.061</v>
       </c>
       <c r="M83">
-        <v>3.13618716</v>
+        <v>3.17490552</v>
       </c>
       <c r="N83">
-        <v>-3.07518716</v>
+        <v>-3.11390552</v>
       </c>
       <c r="O83">
-        <v>-0.5227818172000001</v>
+        <v>-0.5293639384000001</v>
       </c>
       <c r="P83">
-        <v>-2.5524053428</v>
+        <v>-2.5845415816</v>
       </c>
       <c r="Q83">
-        <v>-2.0964053428</v>
+        <v>-2.1285415816</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8737217468991242</v>
+        <v>0.9197173995046312</v>
       </c>
       <c r="T83">
-        <v>2.965052611093576</v>
+        <v>3.129777756154331</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.00330656286469842</v>
+        <v>0.003266238927324049</v>
       </c>
       <c r="W83">
-        <v>0.2350203124765041</v>
+        <v>0.235029820860937</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0194503697923436</v>
+        <v>0.01921317016072965</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.358273585016802</v>
+        <v>0.3601735850168019</v>
       </c>
       <c r="C84">
-        <v>-4.416107126094241</v>
+        <v>-4.634225321732448</v>
       </c>
       <c r="D84">
-        <v>8.921292873905758</v>
+        <v>8.867374678267552</v>
       </c>
       <c r="E84">
-        <v>11.6444</v>
+        <v>11.8086</v>
       </c>
       <c r="F84">
-        <v>13.4644</v>
+        <v>13.6286</v>
       </c>
       <c r="G84">
         <v>0.127</v>
@@ -8163,37 +8163,37 @@
         <v>0.061</v>
       </c>
       <c r="M84">
-        <v>3.17490552</v>
+        <v>3.21362388</v>
       </c>
       <c r="N84">
-        <v>-3.11390552</v>
+        <v>-3.15262388</v>
       </c>
       <c r="O84">
-        <v>-0.5293639384000001</v>
+        <v>-0.5359460596000001</v>
       </c>
       <c r="P84">
-        <v>-2.5845415816</v>
+        <v>-2.6166778204</v>
       </c>
       <c r="Q84">
-        <v>-2.1285415816</v>
+        <v>-2.1606778204</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.9197173995046312</v>
+        <v>0.9711243053578449</v>
       </c>
       <c r="T84">
-        <v>3.129777756154331</v>
+        <v>3.313882330045762</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.003266238927324049</v>
+        <v>0.003226886651091229</v>
       </c>
       <c r="W84">
-        <v>0.235029820860937</v>
+        <v>0.2350391001276727</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.01921317016072965</v>
+        <v>0.01898168618288953</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3601735850168019</v>
+        <v>0.362073585016802</v>
       </c>
       <c r="C85">
-        <v>-4.634225321732448</v>
+        <v>-4.851695694874151</v>
       </c>
       <c r="D85">
-        <v>8.867374678267552</v>
+        <v>8.814104305125849</v>
       </c>
       <c r="E85">
-        <v>11.8086</v>
+        <v>11.9728</v>
       </c>
       <c r="F85">
-        <v>13.6286</v>
+        <v>13.7928</v>
       </c>
       <c r="G85">
         <v>0.127</v>
@@ -8245,37 +8245,37 @@
         <v>0.061</v>
       </c>
       <c r="M85">
-        <v>3.21362388</v>
+        <v>3.25234224</v>
       </c>
       <c r="N85">
-        <v>-3.15262388</v>
+        <v>-3.19134224</v>
       </c>
       <c r="O85">
-        <v>-0.5359460596000001</v>
+        <v>-0.5425281808000001</v>
       </c>
       <c r="P85">
-        <v>-2.6166778204</v>
+        <v>-2.6488140592</v>
       </c>
       <c r="Q85">
-        <v>-2.1606778204</v>
+        <v>-2.1928140592</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9711243053578449</v>
+        <v>1.028957074442711</v>
       </c>
       <c r="T85">
-        <v>3.313882330045762</v>
+        <v>3.520999975673623</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.003226886651091229</v>
+        <v>0.003188471333816334</v>
       </c>
       <c r="W85">
-        <v>0.2350391001276727</v>
+        <v>0.2350481584594861</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.01898168618288953</v>
+        <v>0.0187557137283314</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3620735850168019</v>
+        <v>0.3639735850168019</v>
       </c>
       <c r="C86">
-        <v>-4.851695694874145</v>
+        <v>-5.068529851096933</v>
       </c>
       <c r="D86">
-        <v>8.814104305125852</v>
+        <v>8.761470148903063</v>
       </c>
       <c r="E86">
-        <v>11.9728</v>
+        <v>12.137</v>
       </c>
       <c r="F86">
-        <v>13.7928</v>
+        <v>13.957</v>
       </c>
       <c r="G86">
         <v>0.127</v>
@@ -8327,37 +8327,37 @@
         <v>0.061</v>
       </c>
       <c r="M86">
-        <v>3.252342239999999</v>
+        <v>3.291060599999999</v>
       </c>
       <c r="N86">
-        <v>-3.19134224</v>
+        <v>-3.230060599999999</v>
       </c>
       <c r="O86">
-        <v>-0.5425281808</v>
+        <v>-0.5491103019999999</v>
       </c>
       <c r="P86">
-        <v>-2.648814059199999</v>
+        <v>-2.680950298</v>
       </c>
       <c r="Q86">
-        <v>-2.192814059199999</v>
+        <v>-2.224950298</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.02895707444271</v>
+        <v>1.094500879405557</v>
       </c>
       <c r="T86">
-        <v>3.52099997567362</v>
+        <v>3.755733307385195</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.003188471333816334</v>
+        <v>0.003150959906359671</v>
       </c>
       <c r="W86">
-        <v>0.2350481584594861</v>
+        <v>0.2350570036540804</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.0187557137283314</v>
+        <v>0.01853505827270396</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3639735850168019</v>
+        <v>0.3658735850168019</v>
       </c>
       <c r="C87">
-        <v>-5.068529851096933</v>
+        <v>-5.284739120409309</v>
       </c>
       <c r="D87">
-        <v>8.761470148903063</v>
+        <v>8.709460879590688</v>
       </c>
       <c r="E87">
-        <v>12.137</v>
+        <v>12.3012</v>
       </c>
       <c r="F87">
-        <v>13.957</v>
+        <v>14.1212</v>
       </c>
       <c r="G87">
         <v>0.127</v>
@@ -8409,37 +8409,37 @@
         <v>0.061</v>
       </c>
       <c r="M87">
-        <v>3.291060599999999</v>
+        <v>3.32977896</v>
       </c>
       <c r="N87">
-        <v>-3.230060599999999</v>
+        <v>-3.26877896</v>
       </c>
       <c r="O87">
-        <v>-0.5491103019999999</v>
+        <v>-0.5556924232</v>
       </c>
       <c r="P87">
-        <v>-2.680950298</v>
+        <v>-2.7130865368</v>
       </c>
       <c r="Q87">
-        <v>-2.224950298</v>
+        <v>-2.2570865368</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.094500879405557</v>
+        <v>1.169408085077383</v>
       </c>
       <c r="T87">
-        <v>3.755733307385195</v>
+        <v>4.023999972198424</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.003150959906359671</v>
+        <v>0.00311432083768107</v>
       </c>
       <c r="W87">
-        <v>0.2350570036540804</v>
+        <v>0.2350656431464748</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.01853505827270396</v>
+        <v>0.01831953433930045</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3658735850168019</v>
+        <v>0.3677735850168019</v>
       </c>
       <c r="C88">
-        <v>-5.284739120409309</v>
+        <v>-5.500334565381475</v>
       </c>
       <c r="D88">
-        <v>8.709460879590688</v>
+        <v>8.658065434618521</v>
       </c>
       <c r="E88">
-        <v>12.3012</v>
+        <v>12.4654</v>
       </c>
       <c r="F88">
-        <v>14.1212</v>
+        <v>14.2854</v>
       </c>
       <c r="G88">
         <v>0.127</v>
@@ -8491,37 +8491,37 @@
         <v>0.061</v>
       </c>
       <c r="M88">
-        <v>3.32977896</v>
+        <v>3.368497319999999</v>
       </c>
       <c r="N88">
-        <v>-3.26877896</v>
+        <v>-3.30749732</v>
       </c>
       <c r="O88">
-        <v>-0.5556924232</v>
+        <v>-0.5622745443999999</v>
       </c>
       <c r="P88">
-        <v>-2.7130865368</v>
+        <v>-2.745222775599999</v>
       </c>
       <c r="Q88">
-        <v>-2.2570865368</v>
+        <v>-2.289222775599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.169408085077383</v>
+        <v>1.255839476237181</v>
       </c>
       <c r="T88">
-        <v>4.023999972198424</v>
+        <v>4.333538431598302</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.00311432083768107</v>
+        <v>0.003078524046443357</v>
       </c>
       <c r="W88">
-        <v>0.2350656431464748</v>
+        <v>0.2350740840298487</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.01831953433930045</v>
+        <v>0.01810896497907855</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3677735850168019</v>
+        <v>0.3696735850168019</v>
       </c>
       <c r="C89">
-        <v>-5.500334565381475</v>
+        <v>-5.715326988989972</v>
       </c>
       <c r="D89">
-        <v>8.658065434618521</v>
+        <v>8.607273011010026</v>
       </c>
       <c r="E89">
-        <v>12.4654</v>
+        <v>12.6296</v>
       </c>
       <c r="F89">
-        <v>14.2854</v>
+        <v>14.4496</v>
       </c>
       <c r="G89">
         <v>0.127</v>
@@ -8573,37 +8573,37 @@
         <v>0.061</v>
       </c>
       <c r="M89">
-        <v>3.368497319999999</v>
+        <v>3.40721568</v>
       </c>
       <c r="N89">
-        <v>-3.30749732</v>
+        <v>-3.34621568</v>
       </c>
       <c r="O89">
-        <v>-0.5622745443999999</v>
+        <v>-0.5688566656</v>
       </c>
       <c r="P89">
-        <v>-2.745222775599999</v>
+        <v>-2.7773590144</v>
       </c>
       <c r="Q89">
-        <v>-2.289222775599999</v>
+        <v>-2.3213590144</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.255839476237181</v>
+        <v>1.356676099256947</v>
       </c>
       <c r="T89">
-        <v>4.333538431598302</v>
+        <v>4.694666634231495</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.003078524046443357</v>
+        <v>0.003043540818642864</v>
       </c>
       <c r="W89">
-        <v>0.2350740840298487</v>
+        <v>0.235082333074964</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.01810896497907855</v>
+        <v>0.01790318128613444</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3696735850168019</v>
+        <v>0.3715735850168019</v>
       </c>
       <c r="C90">
-        <v>-5.715326988989972</v>
+        <v>-5.929726942187759</v>
       </c>
       <c r="D90">
-        <v>8.607273011010026</v>
+        <v>8.557073057812239</v>
       </c>
       <c r="E90">
-        <v>12.6296</v>
+        <v>12.7938</v>
       </c>
       <c r="F90">
-        <v>14.4496</v>
+        <v>14.6138</v>
       </c>
       <c r="G90">
         <v>0.127</v>
@@ -8655,37 +8655,37 @@
         <v>0.061</v>
       </c>
       <c r="M90">
-        <v>3.40721568</v>
+        <v>3.44593404</v>
       </c>
       <c r="N90">
-        <v>-3.34621568</v>
+        <v>-3.38493404</v>
       </c>
       <c r="O90">
-        <v>-0.5688566656</v>
+        <v>-0.5754387868</v>
       </c>
       <c r="P90">
-        <v>-2.7773590144</v>
+        <v>-2.8094952532</v>
       </c>
       <c r="Q90">
-        <v>-2.3213590144</v>
+        <v>-2.3534952532</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.356676099256947</v>
+        <v>1.475846653734851</v>
       </c>
       <c r="T90">
-        <v>4.694666634231495</v>
+        <v>5.121454510070722</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.003043540818642864</v>
+        <v>0.003009343730792944</v>
       </c>
       <c r="W90">
-        <v>0.235082333074964</v>
+        <v>0.235090396748279</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.01790318128613444</v>
+        <v>0.01770202194584081</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3715735850168019</v>
+        <v>0.3734735850168019</v>
       </c>
       <c r="C91">
-        <v>-5.929726942187759</v>
+        <v>-6.143544731210971</v>
       </c>
       <c r="D91">
-        <v>8.557073057812239</v>
+        <v>8.507455268789027</v>
       </c>
       <c r="E91">
-        <v>12.7938</v>
+        <v>12.958</v>
       </c>
       <c r="F91">
-        <v>14.6138</v>
+        <v>14.778</v>
       </c>
       <c r="G91">
         <v>0.127</v>
@@ -8737,37 +8737,37 @@
         <v>0.061</v>
       </c>
       <c r="M91">
-        <v>3.44593404</v>
+        <v>3.4846524</v>
       </c>
       <c r="N91">
-        <v>-3.38493404</v>
+        <v>-3.4236524</v>
       </c>
       <c r="O91">
-        <v>-0.5754387868</v>
+        <v>-0.5820209080000001</v>
       </c>
       <c r="P91">
-        <v>-2.8094952532</v>
+        <v>-2.841631492</v>
       </c>
       <c r="Q91">
-        <v>-2.3534952532</v>
+        <v>-2.385631492</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.475846653734851</v>
+        <v>1.618851319108336</v>
       </c>
       <c r="T91">
-        <v>5.121454510070722</v>
+        <v>5.633599961077794</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.003009343730792944</v>
+        <v>0.002975906578228578</v>
       </c>
       <c r="W91">
-        <v>0.235090396748279</v>
+        <v>0.2350982812288537</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.01770202194584081</v>
+        <v>0.01750533281310929</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3734735850168019</v>
+        <v>0.375373585016802</v>
       </c>
       <c r="C92">
-        <v>-6.143544731210971</v>
+        <v>-6.356790424632898</v>
       </c>
       <c r="D92">
-        <v>8.507455268789027</v>
+        <v>8.458409575367101</v>
       </c>
       <c r="E92">
-        <v>12.958</v>
+        <v>13.1222</v>
       </c>
       <c r="F92">
-        <v>14.778</v>
+        <v>14.9422</v>
       </c>
       <c r="G92">
         <v>0.127</v>
@@ -8819,37 +8819,37 @@
         <v>0.061</v>
       </c>
       <c r="M92">
-        <v>3.4846524</v>
+        <v>3.52337076</v>
       </c>
       <c r="N92">
-        <v>-3.4236524</v>
+        <v>-3.46237076</v>
       </c>
       <c r="O92">
-        <v>-0.5820209080000001</v>
+        <v>-0.5886030292000001</v>
       </c>
       <c r="P92">
-        <v>-2.841631492</v>
+        <v>-2.8737677308</v>
       </c>
       <c r="Q92">
-        <v>-2.385631492</v>
+        <v>-2.4177677308</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.618851319108336</v>
+        <v>1.793634799009262</v>
       </c>
       <c r="T92">
-        <v>5.633599961077794</v>
+        <v>6.259555512308661</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.002975906578228578</v>
+        <v>0.002943204308138153</v>
       </c>
       <c r="W92">
-        <v>0.2350982812288537</v>
+        <v>0.235105992424141</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.01750533281310929</v>
+        <v>0.0173129665184597</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.375373585016802</v>
+        <v>0.377273585016802</v>
       </c>
       <c r="C93">
-        <v>-6.356790424632898</v>
+        <v>-6.56947386017538</v>
       </c>
       <c r="D93">
-        <v>8.458409575367101</v>
+        <v>8.409926139824618</v>
       </c>
       <c r="E93">
-        <v>13.1222</v>
+        <v>13.2864</v>
       </c>
       <c r="F93">
-        <v>14.9422</v>
+        <v>15.1064</v>
       </c>
       <c r="G93">
         <v>0.127</v>
@@ -8901,37 +8901,37 @@
         <v>0.061</v>
       </c>
       <c r="M93">
-        <v>3.52337076</v>
+        <v>3.56208912</v>
       </c>
       <c r="N93">
-        <v>-3.46237076</v>
+        <v>-3.50108912</v>
       </c>
       <c r="O93">
-        <v>-0.5886030292000001</v>
+        <v>-0.5951851504000001</v>
       </c>
       <c r="P93">
-        <v>-2.8737677308</v>
+        <v>-2.9059039696</v>
       </c>
       <c r="Q93">
-        <v>-2.4177677308</v>
+        <v>-2.4499039696</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.793634799009262</v>
+        <v>2.012114148885421</v>
       </c>
       <c r="T93">
-        <v>6.259555512308661</v>
+        <v>7.041999951347246</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.002943204308138153</v>
+        <v>0.002911212956962739</v>
       </c>
       <c r="W93">
-        <v>0.235105992424141</v>
+        <v>0.2351135359847482</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.0173129665184597</v>
+        <v>0.01712478209978086</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.377273585016802</v>
+        <v>0.3791735850168019</v>
       </c>
       <c r="C94">
-        <v>-6.56947386017538</v>
+        <v>-6.781604651287283</v>
       </c>
       <c r="D94">
-        <v>8.409926139824618</v>
+        <v>8.361995348712716</v>
       </c>
       <c r="E94">
-        <v>13.2864</v>
+        <v>13.4506</v>
       </c>
       <c r="F94">
-        <v>15.1064</v>
+        <v>15.2706</v>
       </c>
       <c r="G94">
         <v>0.127</v>
@@ -8983,37 +8983,37 @@
         <v>0.061</v>
       </c>
       <c r="M94">
-        <v>3.56208912</v>
+        <v>3.60080748</v>
       </c>
       <c r="N94">
-        <v>-3.50108912</v>
+        <v>-3.53980748</v>
       </c>
       <c r="O94">
-        <v>-0.5951851504000001</v>
+        <v>-0.6017672716000001</v>
       </c>
       <c r="P94">
-        <v>-2.9059039696</v>
+        <v>-2.9380402084</v>
       </c>
       <c r="Q94">
-        <v>-2.4499039696</v>
+        <v>-2.4820402084</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.012114148885421</v>
+        <v>2.293016170154767</v>
       </c>
       <c r="T94">
-        <v>7.041999951347246</v>
+        <v>8.047999944396853</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.002911212956962739</v>
+        <v>0.002879909591834107</v>
       </c>
       <c r="W94">
-        <v>0.2351135359847482</v>
+        <v>0.2351209173182455</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.01712478209978086</v>
+        <v>0.01694064465784773</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3791735850168019</v>
+        <v>0.3810735850168019</v>
       </c>
       <c r="C95">
-        <v>-6.781604651287283</v>
+        <v>-6.99319219349929</v>
       </c>
       <c r="D95">
-        <v>8.361995348712716</v>
+        <v>8.314607806500709</v>
       </c>
       <c r="E95">
-        <v>13.4506</v>
+        <v>13.6148</v>
       </c>
       <c r="F95">
-        <v>15.2706</v>
+        <v>15.4348</v>
       </c>
       <c r="G95">
         <v>0.127</v>
@@ -9065,37 +9065,37 @@
         <v>0.061</v>
       </c>
       <c r="M95">
-        <v>3.60080748</v>
+        <v>3.63952584</v>
       </c>
       <c r="N95">
-        <v>-3.53980748</v>
+        <v>-3.57852584</v>
       </c>
       <c r="O95">
-        <v>-0.6017672716000001</v>
+        <v>-0.6083493928000001</v>
       </c>
       <c r="P95">
-        <v>-2.9380402084</v>
+        <v>-2.9701764472</v>
       </c>
       <c r="Q95">
-        <v>-2.4820402084</v>
+        <v>-2.5141764472</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.293016170154767</v>
+        <v>2.667552198513895</v>
       </c>
       <c r="T95">
-        <v>8.047999944396853</v>
+        <v>9.389333268462998</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.002879909591834107</v>
+        <v>0.002849272255750766</v>
       </c>
       <c r="W95">
-        <v>0.2351209173182455</v>
+        <v>0.235128141602094</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.01694064465784773</v>
+        <v>0.01676042503382802</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3810735850168019</v>
+        <v>0.3829735850168019</v>
       </c>
       <c r="C96">
-        <v>-6.99319219349929</v>
+        <v>-7.204245670563823</v>
       </c>
       <c r="D96">
-        <v>8.314607806500709</v>
+        <v>8.267754329436176</v>
       </c>
       <c r="E96">
-        <v>13.6148</v>
+        <v>13.779</v>
       </c>
       <c r="F96">
-        <v>15.4348</v>
+        <v>15.599</v>
       </c>
       <c r="G96">
         <v>0.127</v>
@@ -9147,37 +9147,37 @@
         <v>0.061</v>
       </c>
       <c r="M96">
-        <v>3.63952584</v>
+        <v>3.6782442</v>
       </c>
       <c r="N96">
-        <v>-3.57852584</v>
+        <v>-3.6172442</v>
       </c>
       <c r="O96">
-        <v>-0.6083493928000001</v>
+        <v>-0.6149315140000001</v>
       </c>
       <c r="P96">
-        <v>-2.9701764472</v>
+        <v>-3.002312686</v>
       </c>
       <c r="Q96">
-        <v>-2.5141764472</v>
+        <v>-2.546312686</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.667552198513895</v>
+        <v>3.191902638216676</v>
       </c>
       <c r="T96">
-        <v>9.389333268462998</v>
+        <v>11.2671999221556</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.002849272255750766</v>
+        <v>0.002819279916216547</v>
       </c>
       <c r="W96">
-        <v>0.235128141602094</v>
+        <v>0.2351352137957561</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.01676042503382802</v>
+        <v>0.01658399950715617</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3829735850168019</v>
+        <v>0.3848735850168019</v>
       </c>
       <c r="C97">
-        <v>-7.204245670563823</v>
+        <v>-7.414774060388558</v>
       </c>
       <c r="D97">
-        <v>8.267754329436176</v>
+        <v>8.221425939611441</v>
       </c>
       <c r="E97">
-        <v>13.779</v>
+        <v>13.9432</v>
       </c>
       <c r="F97">
-        <v>15.599</v>
+        <v>15.7632</v>
       </c>
       <c r="G97">
         <v>0.127</v>
@@ -9229,37 +9229,37 @@
         <v>0.061</v>
       </c>
       <c r="M97">
-        <v>3.6782442</v>
+        <v>3.71696256</v>
       </c>
       <c r="N97">
-        <v>-3.6172442</v>
+        <v>-3.65596256</v>
       </c>
       <c r="O97">
-        <v>-0.6149315140000001</v>
+        <v>-0.6215136352</v>
       </c>
       <c r="P97">
-        <v>-3.002312686</v>
+        <v>-3.0344489248</v>
       </c>
       <c r="Q97">
-        <v>-2.546312686</v>
+        <v>-2.5784489248</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.191902638216676</v>
+        <v>3.978428297770847</v>
       </c>
       <c r="T97">
-        <v>11.2671999221556</v>
+        <v>14.08399990269451</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.002819279916216547</v>
+        <v>0.002789912417089292</v>
       </c>
       <c r="W97">
-        <v>0.2351352137957561</v>
+        <v>0.2351421386520504</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.01658399950715617</v>
+        <v>0.01641124951228989</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3848735850168019</v>
+        <v>0.3867735850168019</v>
       </c>
       <c r="C98">
-        <v>-7.414774060388556</v>
+        <v>-7.624786140771533</v>
       </c>
       <c r="D98">
-        <v>8.221425939611441</v>
+        <v>8.175613859228463</v>
       </c>
       <c r="E98">
-        <v>13.9432</v>
+        <v>14.1074</v>
       </c>
       <c r="F98">
-        <v>15.7632</v>
+        <v>15.9274</v>
       </c>
       <c r="G98">
         <v>0.127</v>
@@ -9311,37 +9311,37 @@
         <v>0.061</v>
       </c>
       <c r="M98">
-        <v>3.71696256</v>
+        <v>3.755680919999999</v>
       </c>
       <c r="N98">
-        <v>-3.65596256</v>
+        <v>-3.694680919999999</v>
       </c>
       <c r="O98">
-        <v>-0.6215136352</v>
+        <v>-0.6280957563999999</v>
       </c>
       <c r="P98">
-        <v>-3.0344489248</v>
+        <v>-3.066585163599999</v>
       </c>
       <c r="Q98">
-        <v>-2.5784489248</v>
+        <v>-2.610585163599999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.978428297770837</v>
+        <v>5.289304397027781</v>
       </c>
       <c r="T98">
-        <v>14.08399990269447</v>
+        <v>18.77866653692596</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.002789912417089292</v>
+        <v>0.002761150433407959</v>
       </c>
       <c r="W98">
-        <v>0.2351421386520504</v>
+        <v>0.2351489207278024</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.01641124951228989</v>
+        <v>0.016242061372988</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3867735850168019</v>
+        <v>0.3886735850168019</v>
       </c>
       <c r="C99">
-        <v>-7.624786140771533</v>
+        <v>-7.834290494945602</v>
       </c>
       <c r="D99">
-        <v>8.175613859228463</v>
+        <v>8.130309505054393</v>
       </c>
       <c r="E99">
-        <v>14.1074</v>
+        <v>14.2716</v>
       </c>
       <c r="F99">
-        <v>15.9274</v>
+        <v>16.0916</v>
       </c>
       <c r="G99">
         <v>0.127</v>
@@ -9393,37 +9393,37 @@
         <v>0.061</v>
       </c>
       <c r="M99">
-        <v>3.755680919999999</v>
+        <v>3.794399279999999</v>
       </c>
       <c r="N99">
-        <v>-3.694680919999999</v>
+        <v>-3.733399279999999</v>
       </c>
       <c r="O99">
-        <v>-0.6280957563999999</v>
+        <v>-0.6346778775999999</v>
       </c>
       <c r="P99">
-        <v>-3.066585163599999</v>
+        <v>-3.098721402399999</v>
       </c>
       <c r="Q99">
-        <v>-2.610585163599999</v>
+        <v>-2.642721402399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.289304397027781</v>
+        <v>7.911056595541673</v>
       </c>
       <c r="T99">
-        <v>18.77866653692596</v>
+        <v>28.16799980538894</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.002761150433407959</v>
+        <v>0.002732975428985429</v>
       </c>
       <c r="W99">
-        <v>0.2351489207278024</v>
+        <v>0.2351555643938452</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.016242061372988</v>
+        <v>0.01607632605285547</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3886735850168019</v>
+        <v>0.3905735850168019</v>
       </c>
       <c r="C100">
-        <v>-7.834290494945602</v>
+        <v>-8.043295516939532</v>
       </c>
       <c r="D100">
-        <v>8.130309505054393</v>
+        <v>8.085504483060465</v>
       </c>
       <c r="E100">
-        <v>14.2716</v>
+        <v>14.4358</v>
       </c>
       <c r="F100">
-        <v>16.0916</v>
+        <v>16.2558</v>
       </c>
       <c r="G100">
         <v>0.127</v>
@@ -9475,37 +9475,37 @@
         <v>0.061</v>
       </c>
       <c r="M100">
-        <v>3.794399279999999</v>
+        <v>3.833117639999999</v>
       </c>
       <c r="N100">
-        <v>-3.733399279999999</v>
+        <v>-3.772117639999999</v>
       </c>
       <c r="O100">
-        <v>-0.6346778775999999</v>
+        <v>-0.6412599988</v>
       </c>
       <c r="P100">
-        <v>-3.098721402399999</v>
+        <v>-3.1308576412</v>
       </c>
       <c r="Q100">
-        <v>-2.642721402399999</v>
+        <v>-2.6748576412</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.911056595541673</v>
+        <v>15.77631319108335</v>
       </c>
       <c r="T100">
-        <v>28.16799980538894</v>
+        <v>56.33599961077789</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.002732975428985429</v>
+        <v>0.002705369616571435</v>
       </c>
       <c r="W100">
-        <v>0.2351555643938452</v>
+        <v>0.2351620738444125</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.01607632605285547</v>
+        <v>0.01591393892100845</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3905735850168019</v>
-      </c>
-      <c r="C101">
-        <v>-8.043295516939532</v>
-      </c>
-      <c r="D101">
-        <v>8.085504483060465</v>
-      </c>
-      <c r="E101">
-        <v>14.4358</v>
-      </c>
-      <c r="F101">
-        <v>16.2558</v>
-      </c>
-      <c r="G101">
-        <v>0.127</v>
-      </c>
-      <c r="H101">
-        <v>14.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.517</v>
-      </c>
-      <c r="K101">
-        <v>0.456</v>
-      </c>
-      <c r="L101">
-        <v>0.061</v>
-      </c>
-      <c r="M101">
-        <v>3.833117639999999</v>
-      </c>
-      <c r="N101">
-        <v>-3.772117639999999</v>
-      </c>
-      <c r="O101">
-        <v>-0.6412599988</v>
-      </c>
-      <c r="P101">
-        <v>-3.1308576412</v>
-      </c>
-      <c r="Q101">
-        <v>-2.6748576412</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>15.77631319108335</v>
-      </c>
-      <c r="T101">
-        <v>56.33599961077789</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.002705369616571435</v>
-      </c>
-      <c r="W101">
-        <v>0.2351620738444125</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.01591393892100845</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
